--- a/backend/static/pulley_pricing_template.xlsx
+++ b/backend/static/pulley_pricing_template.xlsx
@@ -7,12 +7,13 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Pipe Pricing" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Shaft Pricing" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="End Plate Pricing" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Hub Pricing" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="KLA Pricing" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Rubber Lagging Pricing" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="1. Pipe Specs &amp; Pricing" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="2. Shaft Specs &amp; Pricing" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="3. End Plate Pricing" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="4. Hub Pricing" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="5. KLA Pricing" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="6. Rubber Lagging Pricing" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="7. Summary" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,12 +34,30 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00996600"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FF0000"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00666666"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -49,6 +68,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00960018"/>
         <bgColor rgb="00960018"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFBCC"/>
+        <bgColor rgb="00FFFBCC"/>
       </patternFill>
     </fill>
   </fills>
@@ -70,15 +95,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -444,265 +478,297 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="35" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>PULLEY PIPE SPECIFICATIONS &amp; PRICING</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
           <t>Pipe Dia (mm)</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Available Thickness (mm)</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Base Rate (₹/kg)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Rate Increment per mm Thk (₹/kg)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Increment per mm Thk (₹/kg)</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n">
         <v>139</v>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>4.5, 5.4</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr"/>
-      <c r="D2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="C4" s="4" t="inlineStr"/>
+      <c r="D4" s="4" t="inlineStr"/>
+      <c r="E4" s="3" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
         <v>152</v>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>4.8, 5.4</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr"/>
-      <c r="D3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="C5" s="4" t="inlineStr"/>
+      <c r="D5" s="4" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
         <v>168</v>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>4.8, 5.4</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr"/>
-      <c r="D4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="C6" s="4" t="inlineStr"/>
+      <c r="D6" s="4" t="inlineStr"/>
+      <c r="E6" s="3" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
         <v>193</v>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>5.4, 6.3</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr"/>
-      <c r="D5" s="2" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="C7" s="4" t="inlineStr"/>
+      <c r="D7" s="4" t="inlineStr"/>
+      <c r="E7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
         <v>219</v>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>6.3, 8, 10, 12</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr"/>
-      <c r="D6" s="2" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="C8" s="4" t="inlineStr"/>
+      <c r="D8" s="4" t="inlineStr"/>
+      <c r="E8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
         <v>245</v>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>6.3, 8, 10, 12</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr"/>
-      <c r="D7" s="2" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="C9" s="4" t="inlineStr"/>
+      <c r="D9" s="4" t="inlineStr"/>
+      <c r="E9" s="3" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
         <v>273</v>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>6.3, 8, 10, 12</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr"/>
-      <c r="D8" s="2" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="C10" s="4" t="inlineStr"/>
+      <c r="D10" s="4" t="inlineStr"/>
+      <c r="E10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
         <v>323</v>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>6.3, 8, 10, 12, 14</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr"/>
-      <c r="D9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="C11" s="4" t="inlineStr"/>
+      <c r="D11" s="4" t="inlineStr"/>
+      <c r="E11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
         <v>355</v>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>8, 10, 12, 14</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr"/>
-      <c r="D10" s="2" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="C12" s="4" t="inlineStr"/>
+      <c r="D12" s="4" t="inlineStr"/>
+      <c r="E12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
         <v>406</v>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>8, 10, 12, 14, 16, 18</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr"/>
-      <c r="D11" s="2" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="C13" s="4" t="inlineStr"/>
+      <c r="D13" s="4" t="inlineStr"/>
+      <c r="E13" s="3" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
         <v>455</v>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>8, 10, 12, 14, 16, 18</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr"/>
-      <c r="D12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="C14" s="4" t="inlineStr"/>
+      <c r="D14" s="4" t="inlineStr"/>
+      <c r="E14" s="3" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
         <v>508</v>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>8, 10, 12, 14, 16, 18</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr"/>
-      <c r="D13" s="2" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="C15" s="4" t="inlineStr"/>
+      <c r="D15" s="4" t="inlineStr"/>
+      <c r="E15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
         <v>609</v>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>8, 10, 12, 14, 16, 18, 20</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr"/>
-      <c r="D14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="C16" s="4" t="inlineStr"/>
+      <c r="D16" s="4" t="inlineStr"/>
+      <c r="E16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
         <v>630</v>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>8, 10, 12, 14, 16, 18, 20, 22</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr"/>
-      <c r="D15" s="2" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="C17" s="4" t="inlineStr"/>
+      <c r="D17" s="4" t="inlineStr"/>
+      <c r="E17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n">
         <v>800</v>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>8, 10, 12, 14, 16, 18, 20, 22, 24</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr"/>
-      <c r="D16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="C18" s="4" t="inlineStr"/>
+      <c r="D18" s="4" t="inlineStr"/>
+      <c r="E18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>8, 10, 12, 14, 16, 18, 20, 22, 24, 26</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr"/>
-      <c r="D17" s="2" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>INSTRUCTIONS:</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>1. Enter Base Rate (₹/kg) for each pipe diameter</t>
-        </is>
-      </c>
+      <c r="C19" s="4" t="inlineStr"/>
+      <c r="D19" s="4" t="inlineStr"/>
+      <c r="E19" s="3" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2. Enter Rate Increment per mm of thickness (₹/kg)</t>
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>FORMULA:</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3. Formula: Final Rate = Base Rate + (Thickness × Increment)</t>
+          <t>Final Rate (₹/kg) = Base Rate + (Thickness × Increment)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>4. Example: If Base=65, Increment=0.5, Thk=10mm → Rate = 65 + (10 × 0.5) = ₹70/kg</t>
+          <t>Pipe Weight (kg) = π × ((OD² - ID²) / 4) × Length × 7.85 / 1000000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Pipe Cost = Pipe Weight × Final Rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Yellow cells = Enter your values</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -713,68 +779,177 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>Material Grade</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>Base Rate (₹/kg)</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>MS (Mild Steel)</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr"/>
-      <c r="C2" s="2" t="inlineStr"/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>PULLEY SHAFT SPECIFICATIONS &amp; PRICING</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>EN-8</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr"/>
-      <c r="C3" s="2" t="inlineStr"/>
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>MATERIAL GRADES &amp; RATES</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>Material Grade</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Rate (₹/kg)</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>MS (Mild Steel)</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr"/>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Standard mild steel</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>EN-8</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr"/>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Medium carbon steel</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
           <t>EN-9</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr"/>
-      <c r="C4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr"/>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>High carbon steel</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>EN-19</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr"/>
-      <c r="C5" s="2" t="inlineStr"/>
+      <c r="B8" s="4" t="inlineStr"/>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Alloy steel - high strength</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>SHAFT DIMENSIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Shaft Dia @ Centre:</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>50, 55, 60, 65... 300 mm (5mm increments)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Shaft Dia @ Bearing:</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>25, 30, 35, 40... 290 mm (5mm increments)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Constraint:</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Bearing Dia must always be LESS than Centre Dia</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Shaft Length:</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Manual entry by user</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>FORMULA:</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Shaft Weight (kg) = π × (Dia² / 4) × Length × 7.85 / 1000000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Shaft Cost = Shaft Weight × Material Rate</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -785,116 +960,224 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>END PLATE SPECIFICATIONS &amp; PRICING</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Material: MS (Mild Steel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Diameter: Same as selected Pipe Diameter</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>MS Rate (₹/kg):</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>AVAILABLE THICKNESSES</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Thickness (mm)</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>Rate (₹/kg)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="B2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="B10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="B3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="B11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="B4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="B12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="B5" s="2" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="B13" s="3" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="B6" s="2" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="B14" s="3" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="B7" s="2" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="B15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="B8" s="2" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="B16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="B9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="B17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="B10" s="2" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="B18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="B20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="B12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="B21" s="3" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="B13" s="2" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="B22" s="3" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="B14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="B23" s="3" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="B24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
         <v>36</v>
       </c>
-      <c r="B15" s="2" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="B25" s="3" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="B26" s="3" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="B16" s="2" t="inlineStr"/>
+      <c r="B27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="B28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="B29" s="3" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="B30" s="3" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="B31" s="3" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="B32" s="3" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>FORMULA:</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>End Plate Weight = π × (Dia² / 4) × Thickness × 7.85 / 1000000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>End Plate Cost = Weight × MS Rate × 2 (for 2 plates)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -905,28 +1188,309 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:C52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>Hub Rate (₹/kg)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Enter rate:</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>HUB SPECIFICATIONS &amp; PRICING</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Material: MS (Mild Steel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Options: No Hub / With Hub</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>MS Rate (₹/kg):</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>HUB DIMENSIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Hub Diameter (mm)</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>110</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>140</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
+        <v>160</v>
+      </c>
+      <c r="B16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>170</v>
+      </c>
+      <c r="B17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n">
+        <v>180</v>
+      </c>
+      <c r="B18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>190</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="B20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>210</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="n">
+        <v>220</v>
+      </c>
+      <c r="B22" s="3" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
+        <v>230</v>
+      </c>
+      <c r="B23" s="3" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="n">
+        <v>240</v>
+      </c>
+      <c r="B24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>250</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="n">
+        <v>260</v>
+      </c>
+      <c r="B26" s="3" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n">
+        <v>270</v>
+      </c>
+      <c r="B27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="n">
+        <v>280</v>
+      </c>
+      <c r="B28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n">
+        <v>290</v>
+      </c>
+      <c r="B29" s="3" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="B30" s="3" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n">
+        <v>310</v>
+      </c>
+      <c r="B31" s="3" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="n">
+        <v>320</v>
+      </c>
+      <c r="B32" s="3" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>330</v>
+      </c>
+      <c r="B33" s="3" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="n">
+        <v>340</v>
+      </c>
+      <c r="B34" s="3" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>350</v>
+      </c>
+      <c r="B35" s="3" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="n">
+        <v>360</v>
+      </c>
+      <c r="B36" s="3" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n">
+        <v>370</v>
+      </c>
+      <c r="B37" s="3" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="n">
+        <v>380</v>
+      </c>
+      <c r="B38" s="3" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="n">
+        <v>390</v>
+      </c>
+      <c r="B39" s="3" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="n">
+        <v>400</v>
+      </c>
+      <c r="B40" s="3" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="n">
+        <v>410</v>
+      </c>
+      <c r="B41" s="3" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="n">
+        <v>420</v>
+      </c>
+      <c r="B42" s="3" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="n">
+        <v>430</v>
+      </c>
+      <c r="B43" s="3" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="n">
+        <v>440</v>
+      </c>
+      <c r="B44" s="3" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="n">
+        <v>450</v>
+      </c>
+      <c r="B45" s="3" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Hub Length: Manual entry by user</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>FORMULA:</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Hub Weight = π × ((OD² - ID²) / 4) × Length × 7.85 / 1000000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Hub Cost = Hub Weight × MS Rate</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -937,39 +1501,175 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>KLA (KEYLESS LOCKING ASSEMBLY) PRICING</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>(To be filled later)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>KLA Model</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>Shaft Dia @ Brg (mm)</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Min Shaft Dia @ Brg (mm)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Max Shaft Dia @ Brg (mm)</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Price (₹/unit)</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>(Add models here)</t>
-        </is>
-      </c>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr"/>
+      <c r="B6" s="4" t="inlineStr"/>
+      <c r="C6" s="4" t="inlineStr"/>
+      <c r="D6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr"/>
+      <c r="B7" s="4" t="inlineStr"/>
+      <c r="C7" s="4" t="inlineStr"/>
+      <c r="D7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr"/>
+      <c r="B8" s="4" t="inlineStr"/>
+      <c r="C8" s="4" t="inlineStr"/>
+      <c r="D8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr"/>
+      <c r="B9" s="4" t="inlineStr"/>
+      <c r="C9" s="4" t="inlineStr"/>
+      <c r="D9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr"/>
+      <c r="B10" s="4" t="inlineStr"/>
+      <c r="C10" s="4" t="inlineStr"/>
+      <c r="D10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr"/>
+      <c r="B11" s="4" t="inlineStr"/>
+      <c r="C11" s="4" t="inlineStr"/>
+      <c r="D11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr"/>
+      <c r="B12" s="4" t="inlineStr"/>
+      <c r="C12" s="4" t="inlineStr"/>
+      <c r="D12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr"/>
+      <c r="B13" s="4" t="inlineStr"/>
+      <c r="C13" s="4" t="inlineStr"/>
+      <c r="D13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr"/>
+      <c r="B14" s="4" t="inlineStr"/>
+      <c r="C14" s="4" t="inlineStr"/>
+      <c r="D14" s="4" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr"/>
+      <c r="B15" s="4" t="inlineStr"/>
+      <c r="C15" s="4" t="inlineStr"/>
+      <c r="D15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr"/>
+      <c r="B16" s="4" t="inlineStr"/>
+      <c r="C16" s="4" t="inlineStr"/>
+      <c r="D16" s="4" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr"/>
+      <c r="B17" s="4" t="inlineStr"/>
+      <c r="C17" s="4" t="inlineStr"/>
+      <c r="D17" s="4" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr"/>
+      <c r="B18" s="4" t="inlineStr"/>
+      <c r="C18" s="4" t="inlineStr"/>
+      <c r="D18" s="4" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr"/>
+      <c r="B19" s="4" t="inlineStr"/>
+      <c r="C19" s="4" t="inlineStr"/>
+      <c r="D19" s="4" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr"/>
+      <c r="B20" s="4" t="inlineStr"/>
+      <c r="C20" s="4" t="inlineStr"/>
+      <c r="D20" s="4" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr"/>
+      <c r="B21" s="4" t="inlineStr"/>
+      <c r="C21" s="4" t="inlineStr"/>
+      <c r="D21" s="4" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr"/>
+      <c r="B22" s="4" t="inlineStr"/>
+      <c r="C22" s="4" t="inlineStr"/>
+      <c r="D22" s="4" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr"/>
+      <c r="B23" s="4" t="inlineStr"/>
+      <c r="C23" s="4" t="inlineStr"/>
+      <c r="D23" s="4" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr"/>
+      <c r="B24" s="4" t="inlineStr"/>
+      <c r="C24" s="4" t="inlineStr"/>
+      <c r="D24" s="4" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr"/>
+      <c r="B25" s="4" t="inlineStr"/>
+      <c r="C25" s="4" t="inlineStr"/>
+      <c r="D25" s="4" t="inlineStr"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -980,71 +1680,564 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>RUBBER LAGGING PRICING</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Pricing: Per Square Meter (₹/sqm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Area = π × Pipe Diameter × Pipe Length</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>PLAIN / DIAMOND LAGGING</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>(Same rate for both types)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Thickness (mm)</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>Rate (₹/sqm or ₹/unit)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Plain</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>8, 10, 12, 14, 16, 18, 20</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr"/>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Rate (₹/sqm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B14" s="4" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" s="4" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>CERAMIC LAGGING</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Thickness (mm)</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Rate (₹/sqm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B20" s="4" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" s="4" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B22" s="4" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>FORMULA:</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Lagging Area (sqm) = π × Pipe Dia × Pipe Length / 1000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Lagging Cost = Area × Rate per sqm</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C39"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>PULLEY CONFIGURATION SUMMARY</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Diamond</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>8, 10, 12, 14, 16, 18, 20</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr"/>
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>PULLEY TYPES</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Drive, Tail, Bend, Snub, Take-up</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Ceramic</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>12, 15, 22</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr"/>
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>PIPE</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Diameters</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>139, 152, 168, 193, 219, 245, 273, 323, 355, 406, 455, 508, 609, 630, 800, 1000 mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Thickness</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Varies by diameter (see Sheet 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Length</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Manual entry</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Pricing</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Weight × (Base Rate + Thk × Increment)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>SHAFT</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Materials</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>MS, EN-8, EN-9, EN-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Dia @ Centre</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>50 to 300 mm (5mm gaps)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Dia @ Bearing</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>25 to 290 mm (5mm gaps, always &lt; Centre)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Length</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Manual entry</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Pricing</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Weight × Material Rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>END PLATE</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Material</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Diameter</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Same as Pipe Diameter</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Thickness</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>6 to 50 mm (2mm gaps)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Pricing</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Weight × MS Rate × 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>HUB</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Options</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>No Hub / With Hub</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Material</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Diameter</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>100 to 450 mm (10mm gaps)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Length</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Manual entry</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Pricing</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Weight × MS Rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>KLA</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Models</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>To be provided later</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Pricing</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Fixed price per model</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>RUBBER LAGGING</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Options</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>None / Plain / Diamond / Ceramic</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Plain/Diamond Thk</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>8, 10, 12, 14, 16, 18, 20 mm (same rates)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Ceramic Thk</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>12, 15, 22 mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Pricing</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Area × Rate per sqm</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/backend/static/pulley_pricing_template.xlsx
+++ b/backend/static/pulley_pricing_template.xlsx
@@ -8,11 +8,13 @@
   </bookViews>
   <sheets>
     <sheet name="1. Pipe Pricing (FILLED)" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="2. Shaft Pricing (TO FILL)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="3. End Plate (TO FILL)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="4. Hub Pricing (TO FILL)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="5. KLA (TO FILL LATER)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="6. Rubber Lagging (TO FILL)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="2. Shaft Dia @ Centre" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="3. Shaft Dia @ Bearing" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="4. Shaft Material Rates" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="5. End Plate Pricing" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="6. Hub Pricing" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="7. KLA (LATER)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="8. Rubber Lagging" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -41,13 +43,15 @@
       <sz val="11"/>
     </font>
     <font>
-      <color rgb="00228B22"/>
+      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00FF0000"/>
     </font>
     <font>
-      <color rgb="00FF0000"/>
+      <b val="1"/>
+      <color rgb="00996600"/>
     </font>
   </fonts>
   <fills count="5">
@@ -109,10 +113,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -479,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O23"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1533,20 +1537,6 @@
         <v>99</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>✓ Green cells = Filled data</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>- = Not applicable for this combination</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>
@@ -1561,128 +1551,450 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:B57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SHAFT MATERIAL RATES (₹/kg)</t>
+          <t>SHAFT DIA @ CENTRE (50-300mm, 5mm gaps)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Material Grade</t>
+          <t>Sr. No.</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Rate (₹/kg)</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Description</t>
+          <t>Shaft Dia @ Centre (mm)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>MS (Mild Steel)</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr"/>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Standard mild steel</t>
-        </is>
+      <c r="A4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="4" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>EN-8</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr"/>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Medium carbon steel</t>
-        </is>
+      <c r="A5" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>55</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>EN-9</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr"/>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>High carbon steel</t>
-        </is>
+      <c r="A6" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>EN-19</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr"/>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Alloy steel - high strength</t>
-        </is>
+      <c r="A7" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>75</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>SHAFT DIMENSIONS:</t>
-        </is>
+      <c r="A10" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Dia @ Centre: 50, 55, 60... 300mm (5mm gaps)</t>
-        </is>
+      <c r="A11" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>85</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Dia @ Bearing: 25, 30, 35... 290mm (5mm gaps)</t>
-        </is>
+      <c r="A12" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Length: Manual entry</t>
-        </is>
+      <c r="A13" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>95</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>Note: Bearing Dia &lt; Centre Dia (always)</t>
+      <c r="A14" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B23" s="4" t="n">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" s="4" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B25" s="4" t="n">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="B26" s="4" t="n">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="B27" s="4" t="n">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="B28" s="4" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="B29" s="4" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="B30" s="4" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="B31" s="4" t="n">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="B32" s="4" t="n">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="B33" s="4" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="B34" s="4" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="B35" s="4" t="n">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="B36" s="4" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="B37" s="4" t="n">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="B38" s="4" t="n">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="B39" s="4" t="n">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="B40" s="4" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="B41" s="4" t="n">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="B42" s="4" t="n">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="B43" s="4" t="n">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="B44" s="4" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="B45" s="4" t="n">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="B46" s="4" t="n">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="B47" s="4" t="n">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="B48" s="4" t="n">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="B49" s="4" t="n">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="B50" s="4" t="n">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="B51" s="4" t="n">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="B52" s="4" t="n">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="B53" s="4" t="n">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="B54" s="4" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>Total: 51 sizes</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A1:B1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1694,53 +2006,475 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>END PLATE PRICING</t>
+          <t>SHAFT DIA @ BEARING (25-290mm, 5mm gaps)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Material: MS (Mild Steel)</t>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Sr. No.</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Shaft Dia @ Bearing (mm)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Diameter: Same as Pipe Diameter</t>
-        </is>
+      <c r="A4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="4" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>MS Rate (₹/kg):</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr"/>
+      <c r="A6" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>Thicknesses available:</t>
-        </is>
+      <c r="A8" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>45</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>6, 8, 10, 12, 14, 16, 18, 20, 22, 24, 26, 28, 30, 32, 34, 36, 38, 40, 42, 44, 46, 48, 50 mm</t>
+      <c r="A9" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B23" s="4" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" s="4" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B25" s="4" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="B26" s="4" t="n">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="B27" s="4" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="B28" s="4" t="n">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="B29" s="4" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="B30" s="4" t="n">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="B31" s="4" t="n">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="B32" s="4" t="n">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="B33" s="4" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="B34" s="4" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="B35" s="4" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="B36" s="4" t="n">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="B37" s="4" t="n">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="B38" s="4" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="B39" s="4" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="B40" s="4" t="n">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="B41" s="4" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="B42" s="4" t="n">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="B43" s="4" t="n">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="B44" s="4" t="n">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="B45" s="4" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="B46" s="4" t="n">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="B47" s="4" t="n">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="B48" s="4" t="n">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="B49" s="4" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="B50" s="4" t="n">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="B51" s="4" t="n">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="B52" s="4" t="n">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="B53" s="4" t="n">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="B54" s="4" t="n">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="B55" s="4" t="n">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="n">
+        <v>53</v>
+      </c>
+      <c r="B56" s="4" t="n">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="n">
+        <v>54</v>
+      </c>
+      <c r="B57" s="4" t="n">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>Total: 54 sizes</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>NOTE: Bearing Dia must always be LESS than Centre Dia</t>
         </is>
       </c>
     </row>
@@ -1758,66 +2492,100 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>HUB PRICING</t>
+          <t>SHAFT MATERIAL RATES (₹/kg) - TO FILL</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Material: MS (Mild Steel)</t>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Material Grade</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Rate (₹/kg)</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Description</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Options: No Hub / With Hub</t>
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>MS (Mild Steel)</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr"/>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Standard mild steel</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>EN-8</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr"/>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Medium carbon steel</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>MS Rate (₹/kg):</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>Hub Diameters:</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>100, 110, 120... 450mm (10mm gaps)</t>
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>EN-9</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr"/>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>High carbon steel</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>EN-19</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr"/>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Alloy steel - high strength</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Hub Length: Manual entry</t>
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>Yellow cells = Enter your rates</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A1:C1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1829,19 +2597,576 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>KLA (KEYLESS LOCKING ASSEMBLY) - TO BE FILLED LATER</t>
+          <t>END PLATE PRICING - TO FILL</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Material: MS</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Diameter: Same as Pipe Dia</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>MS Rate (₹/kg):</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>THICKNESSES:</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Thickness (mm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>Total: 23 thicknesses</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B48"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>HUB PRICING - TO FILL</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Material: MS</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Options: No Hub / With Hub</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>MS Rate (₹/kg):</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>HUB DIAMETERS:</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Sr. No.</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Hub Dia (mm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B23" s="4" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="B24" s="4" t="n">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="B25" s="4" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="B26" s="4" t="n">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B27" s="4" t="n">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="B28" s="4" t="n">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B29" s="4" t="n">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B30" s="4" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B31" s="4" t="n">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="B32" s="4" t="n">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="B33" s="4" t="n">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="B34" s="4" t="n">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="B35" s="4" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="B36" s="4" t="n">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="B37" s="4" t="n">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="B38" s="4" t="n">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="B39" s="4" t="n">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="B40" s="4" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="B41" s="4" t="n">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="B42" s="4" t="n">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="B43" s="4" t="n">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="B44" s="4" t="n">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="B45" s="4" t="n">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>Total: 36 sizes</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Hub Length: Manual entry by user</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>KLA PRICING - TO FILL LATER</t>
         </is>
       </c>
     </row>
@@ -1853,139 +3178,139 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Min Shaft Dia @ Brg</t>
+          <t>Min Shaft @ Brg</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Max Shaft Dia @ Brg</t>
+          <t>Max Shaft @ Brg</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Price (₹/unit)</t>
+          <t>Price (₹)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr"/>
-      <c r="B4" s="6" t="inlineStr"/>
-      <c r="C4" s="6" t="inlineStr"/>
-      <c r="D4" s="6" t="inlineStr"/>
+      <c r="A4" s="7" t="inlineStr"/>
+      <c r="B4" s="7" t="inlineStr"/>
+      <c r="C4" s="7" t="inlineStr"/>
+      <c r="D4" s="7" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr"/>
-      <c r="B5" s="6" t="inlineStr"/>
-      <c r="C5" s="6" t="inlineStr"/>
-      <c r="D5" s="6" t="inlineStr"/>
+      <c r="A5" s="7" t="inlineStr"/>
+      <c r="B5" s="7" t="inlineStr"/>
+      <c r="C5" s="7" t="inlineStr"/>
+      <c r="D5" s="7" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr"/>
-      <c r="B6" s="6" t="inlineStr"/>
-      <c r="C6" s="6" t="inlineStr"/>
-      <c r="D6" s="6" t="inlineStr"/>
+      <c r="A6" s="7" t="inlineStr"/>
+      <c r="B6" s="7" t="inlineStr"/>
+      <c r="C6" s="7" t="inlineStr"/>
+      <c r="D6" s="7" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr"/>
-      <c r="B7" s="6" t="inlineStr"/>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr"/>
+      <c r="A7" s="7" t="inlineStr"/>
+      <c r="B7" s="7" t="inlineStr"/>
+      <c r="C7" s="7" t="inlineStr"/>
+      <c r="D7" s="7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr"/>
-      <c r="B8" s="6" t="inlineStr"/>
-      <c r="C8" s="6" t="inlineStr"/>
-      <c r="D8" s="6" t="inlineStr"/>
+      <c r="A8" s="7" t="inlineStr"/>
+      <c r="B8" s="7" t="inlineStr"/>
+      <c r="C8" s="7" t="inlineStr"/>
+      <c r="D8" s="7" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr"/>
-      <c r="B9" s="6" t="inlineStr"/>
-      <c r="C9" s="6" t="inlineStr"/>
-      <c r="D9" s="6" t="inlineStr"/>
+      <c r="A9" s="7" t="inlineStr"/>
+      <c r="B9" s="7" t="inlineStr"/>
+      <c r="C9" s="7" t="inlineStr"/>
+      <c r="D9" s="7" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr"/>
-      <c r="B10" s="6" t="inlineStr"/>
-      <c r="C10" s="6" t="inlineStr"/>
-      <c r="D10" s="6" t="inlineStr"/>
+      <c r="A10" s="7" t="inlineStr"/>
+      <c r="B10" s="7" t="inlineStr"/>
+      <c r="C10" s="7" t="inlineStr"/>
+      <c r="D10" s="7" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr"/>
-      <c r="B11" s="6" t="inlineStr"/>
-      <c r="C11" s="6" t="inlineStr"/>
-      <c r="D11" s="6" t="inlineStr"/>
+      <c r="A11" s="7" t="inlineStr"/>
+      <c r="B11" s="7" t="inlineStr"/>
+      <c r="C11" s="7" t="inlineStr"/>
+      <c r="D11" s="7" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr"/>
-      <c r="B12" s="6" t="inlineStr"/>
-      <c r="C12" s="6" t="inlineStr"/>
-      <c r="D12" s="6" t="inlineStr"/>
+      <c r="A12" s="7" t="inlineStr"/>
+      <c r="B12" s="7" t="inlineStr"/>
+      <c r="C12" s="7" t="inlineStr"/>
+      <c r="D12" s="7" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr"/>
-      <c r="B13" s="6" t="inlineStr"/>
-      <c r="C13" s="6" t="inlineStr"/>
-      <c r="D13" s="6" t="inlineStr"/>
+      <c r="A13" s="7" t="inlineStr"/>
+      <c r="B13" s="7" t="inlineStr"/>
+      <c r="C13" s="7" t="inlineStr"/>
+      <c r="D13" s="7" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr"/>
-      <c r="B14" s="6" t="inlineStr"/>
-      <c r="C14" s="6" t="inlineStr"/>
-      <c r="D14" s="6" t="inlineStr"/>
+      <c r="A14" s="7" t="inlineStr"/>
+      <c r="B14" s="7" t="inlineStr"/>
+      <c r="C14" s="7" t="inlineStr"/>
+      <c r="D14" s="7" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr"/>
-      <c r="B15" s="6" t="inlineStr"/>
-      <c r="C15" s="6" t="inlineStr"/>
-      <c r="D15" s="6" t="inlineStr"/>
+      <c r="A15" s="7" t="inlineStr"/>
+      <c r="B15" s="7" t="inlineStr"/>
+      <c r="C15" s="7" t="inlineStr"/>
+      <c r="D15" s="7" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr"/>
-      <c r="B16" s="6" t="inlineStr"/>
-      <c r="C16" s="6" t="inlineStr"/>
-      <c r="D16" s="6" t="inlineStr"/>
+      <c r="A16" s="7" t="inlineStr"/>
+      <c r="B16" s="7" t="inlineStr"/>
+      <c r="C16" s="7" t="inlineStr"/>
+      <c r="D16" s="7" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr"/>
-      <c r="B17" s="6" t="inlineStr"/>
-      <c r="C17" s="6" t="inlineStr"/>
-      <c r="D17" s="6" t="inlineStr"/>
+      <c r="A17" s="7" t="inlineStr"/>
+      <c r="B17" s="7" t="inlineStr"/>
+      <c r="C17" s="7" t="inlineStr"/>
+      <c r="D17" s="7" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr"/>
-      <c r="B18" s="6" t="inlineStr"/>
-      <c r="C18" s="6" t="inlineStr"/>
-      <c r="D18" s="6" t="inlineStr"/>
+      <c r="A18" s="7" t="inlineStr"/>
+      <c r="B18" s="7" t="inlineStr"/>
+      <c r="C18" s="7" t="inlineStr"/>
+      <c r="D18" s="7" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr"/>
-      <c r="B19" s="6" t="inlineStr"/>
-      <c r="C19" s="6" t="inlineStr"/>
-      <c r="D19" s="6" t="inlineStr"/>
+      <c r="A19" s="7" t="inlineStr"/>
+      <c r="B19" s="7" t="inlineStr"/>
+      <c r="C19" s="7" t="inlineStr"/>
+      <c r="D19" s="7" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr"/>
-      <c r="B20" s="6" t="inlineStr"/>
-      <c r="C20" s="6" t="inlineStr"/>
-      <c r="D20" s="6" t="inlineStr"/>
+      <c r="A20" s="7" t="inlineStr"/>
+      <c r="B20" s="7" t="inlineStr"/>
+      <c r="C20" s="7" t="inlineStr"/>
+      <c r="D20" s="7" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr"/>
-      <c r="B21" s="6" t="inlineStr"/>
-      <c r="C21" s="6" t="inlineStr"/>
-      <c r="D21" s="6" t="inlineStr"/>
+      <c r="A21" s="7" t="inlineStr"/>
+      <c r="B21" s="7" t="inlineStr"/>
+      <c r="C21" s="7" t="inlineStr"/>
+      <c r="D21" s="7" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="inlineStr"/>
-      <c r="B22" s="6" t="inlineStr"/>
-      <c r="C22" s="6" t="inlineStr"/>
-      <c r="D22" s="6" t="inlineStr"/>
+      <c r="A22" s="7" t="inlineStr"/>
+      <c r="B22" s="7" t="inlineStr"/>
+      <c r="C22" s="7" t="inlineStr"/>
+      <c r="D22" s="7" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="inlineStr"/>
-      <c r="B23" s="6" t="inlineStr"/>
-      <c r="C23" s="6" t="inlineStr"/>
-      <c r="D23" s="6" t="inlineStr"/>
+      <c r="A23" s="7" t="inlineStr"/>
+      <c r="B23" s="7" t="inlineStr"/>
+      <c r="C23" s="7" t="inlineStr"/>
+      <c r="D23" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1995,7 +3320,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2011,12 +3336,12 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RUBBER LAGGING PRICING (₹/sqm)</t>
+          <t>RUBBER LAGGING PRICING (₹/sqm) - TO FILL</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>PLAIN / DIAMOND (Same rates)</t>
         </is>
@@ -2035,49 +3360,49 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B5" s="6" t="inlineStr"/>
+      <c r="B5" s="7" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B6" s="6" t="inlineStr"/>
+      <c r="B6" s="7" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B7" s="6" t="inlineStr"/>
+      <c r="B7" s="7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B8" s="6" t="inlineStr"/>
+      <c r="B8" s="7" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B9" s="6" t="inlineStr"/>
+      <c r="B9" s="7" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="B10" s="6" t="inlineStr"/>
+      <c r="B10" s="7" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="B11" s="6" t="inlineStr"/>
+      <c r="B11" s="7" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>CERAMIC</t>
         </is>
@@ -2096,22 +3421,22 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="6" t="inlineStr"/>
+      <c r="B16" s="7" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B17" s="6" t="inlineStr"/>
+      <c r="B17" s="7" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="B18" s="6" t="inlineStr"/>
+      <c r="B18" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/backend/static/pulley_pricing_template.xlsx
+++ b/backend/static/pulley_pricing_template.xlsx
@@ -7,14 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="1. Pipe Pricing (FILLED)" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="2. Shaft Dia @ Centre" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="3. Shaft Dia @ Bearing" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="4. Shaft Material Rates" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="5. End Plate Pricing" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="6. Hub Pricing" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="7. KLA (LATER)" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="8. Rubber Lagging" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="1. Pipe Pricing" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="2. Shaft Pricing" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="3. End Plate" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="4. Hub Pricing" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="5. KLA (LATER)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="6. Rubber Lagging" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,14 +42,17 @@
     </font>
     <font>
       <b val="1"/>
+      <sz val="12"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="00FF0000"/>
     </font>
     <font>
+      <color rgb="00996600"/>
+    </font>
+    <font>
       <b val="1"/>
-      <color rgb="00996600"/>
     </font>
   </fonts>
   <fills count="5">
@@ -98,7 +99,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -113,11 +114,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1551,450 +1553,861 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B57"/>
+  <dimension ref="A1:H63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="3" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="3" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SHAFT DIA @ CENTRE (50-300mm, 5mm gaps)</t>
+          <t>SHAFT SPECIFICATIONS &amp; PRICING</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Sr. No.</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Shaft Dia @ Centre (mm)</t>
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>MATERIAL RATES (₹/kg)</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>SHAFT DIA @ CENTRE (mm)</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>SHAFT DIA @ BEARING (mm)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Material Grade</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Rate (₹/kg)</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Sr.</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Dia (mm)</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Sr.</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Dia (mm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>MS (Mild Steel)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr"/>
+      <c r="D5" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="E5" s="4" t="n">
         <v>50</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="G5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>EN-8</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr"/>
+      <c r="D6" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="E6" s="4" t="n">
         <v>55</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="G6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>EN-9</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr"/>
+      <c r="D7" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="E7" s="4" t="n">
         <v>60</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="G7" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>EN-19</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr"/>
+      <c r="D8" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="E8" s="4" t="n">
         <v>65</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="G8" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="D9" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="E9" s="4" t="n">
         <v>70</v>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="G9" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="D10" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="4" t="n">
+      <c r="E10" s="4" t="n">
         <v>75</v>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="G10" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="D11" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="E11" s="4" t="n">
         <v>80</v>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="G11" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="D12" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="4" t="n">
+      <c r="E12" s="4" t="n">
         <v>85</v>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="G12" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="D13" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="B12" s="4" t="n">
+      <c r="E13" s="4" t="n">
         <v>90</v>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="G13" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="D14" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="4" t="n">
+      <c r="E14" s="4" t="n">
         <v>95</v>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="G14" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="D15" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="E15" s="4" t="n">
         <v>100</v>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="G15" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="D16" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="B15" s="4" t="n">
+      <c r="E16" s="4" t="n">
         <v>105</v>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="G16" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="D17" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="B16" s="4" t="n">
+      <c r="E17" s="4" t="n">
         <v>110</v>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="G17" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="D18" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="B17" s="4" t="n">
+      <c r="E18" s="4" t="n">
         <v>115</v>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="G18" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="D19" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="B18" s="4" t="n">
+      <c r="E19" s="4" t="n">
         <v>120</v>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="G19" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="D20" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="B19" s="4" t="n">
+      <c r="E20" s="4" t="n">
         <v>125</v>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="G20" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="D21" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="B20" s="4" t="n">
+      <c r="E21" s="4" t="n">
         <v>130</v>
       </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="G21" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="D22" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="B21" s="4" t="n">
+      <c r="E22" s="4" t="n">
         <v>135</v>
       </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="G22" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="D23" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="B22" s="4" t="n">
+      <c r="E23" s="4" t="n">
         <v>140</v>
       </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="G23" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="D24" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="B23" s="4" t="n">
+      <c r="E24" s="4" t="n">
         <v>145</v>
       </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="G24" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="D25" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="B24" s="4" t="n">
+      <c r="E25" s="4" t="n">
         <v>150</v>
       </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="G25" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="H25" s="4" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="D26" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="B25" s="4" t="n">
+      <c r="E26" s="4" t="n">
         <v>155</v>
       </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="G26" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="D27" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="B26" s="4" t="n">
+      <c r="E27" s="4" t="n">
         <v>160</v>
       </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="G27" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="H27" s="4" t="n">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="D28" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="B27" s="4" t="n">
+      <c r="E28" s="4" t="n">
         <v>165</v>
       </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="G28" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="H28" s="4" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="D29" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="B28" s="4" t="n">
+      <c r="E29" s="4" t="n">
         <v>170</v>
       </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="G29" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="H29" s="4" t="n">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="D30" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="B29" s="4" t="n">
+      <c r="E30" s="4" t="n">
         <v>175</v>
       </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="G30" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="D31" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="B30" s="4" t="n">
+      <c r="E31" s="4" t="n">
         <v>180</v>
       </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="G31" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="H31" s="4" t="n">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="D32" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="B31" s="4" t="n">
+      <c r="E32" s="4" t="n">
         <v>185</v>
       </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="G32" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="H32" s="4" t="n">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="D33" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="B32" s="4" t="n">
+      <c r="E33" s="4" t="n">
         <v>190</v>
       </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="G33" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="H33" s="4" t="n">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="D34" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="B33" s="4" t="n">
+      <c r="E34" s="4" t="n">
         <v>195</v>
       </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="G34" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="H34" s="4" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="D35" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="B34" s="4" t="n">
+      <c r="E35" s="4" t="n">
         <v>200</v>
       </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="G35" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="H35" s="4" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="D36" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="B35" s="4" t="n">
+      <c r="E36" s="4" t="n">
         <v>205</v>
       </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="G36" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="H36" s="4" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="D37" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="B36" s="4" t="n">
+      <c r="E37" s="4" t="n">
         <v>210</v>
       </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="G37" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="H37" s="4" t="n">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="D38" s="3" t="n">
         <v>34</v>
       </c>
-      <c r="B37" s="4" t="n">
+      <c r="E38" s="4" t="n">
         <v>215</v>
       </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="G38" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="H38" s="4" t="n">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="D39" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="B38" s="4" t="n">
+      <c r="E39" s="4" t="n">
         <v>220</v>
       </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="G39" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="H39" s="4" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="D40" s="3" t="n">
         <v>36</v>
       </c>
-      <c r="B39" s="4" t="n">
+      <c r="E40" s="4" t="n">
         <v>225</v>
       </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="G40" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="H40" s="4" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="D41" s="3" t="n">
         <v>37</v>
       </c>
-      <c r="B40" s="4" t="n">
+      <c r="E41" s="4" t="n">
         <v>230</v>
       </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="G41" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="H41" s="4" t="n">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="D42" s="3" t="n">
         <v>38</v>
       </c>
-      <c r="B41" s="4" t="n">
+      <c r="E42" s="4" t="n">
         <v>235</v>
       </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="n">
+      <c r="G42" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="H42" s="4" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="D43" s="3" t="n">
         <v>39</v>
       </c>
-      <c r="B42" s="4" t="n">
+      <c r="E43" s="4" t="n">
         <v>240</v>
       </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="n">
+      <c r="G43" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="H43" s="4" t="n">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="D44" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="B43" s="4" t="n">
+      <c r="E44" s="4" t="n">
         <v>245</v>
       </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="3" t="n">
+      <c r="G44" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="H44" s="4" t="n">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="D45" s="3" t="n">
         <v>41</v>
       </c>
-      <c r="B44" s="4" t="n">
+      <c r="E45" s="4" t="n">
         <v>250</v>
       </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="n">
+      <c r="G45" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="H45" s="4" t="n">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="D46" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="B45" s="4" t="n">
+      <c r="E46" s="4" t="n">
         <v>255</v>
       </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="n">
+      <c r="G46" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="H46" s="4" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="D47" s="3" t="n">
         <v>43</v>
       </c>
-      <c r="B46" s="4" t="n">
+      <c r="E47" s="4" t="n">
         <v>260</v>
       </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="n">
+      <c r="G47" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="H47" s="4" t="n">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="D48" s="3" t="n">
         <v>44</v>
       </c>
-      <c r="B47" s="4" t="n">
+      <c r="E48" s="4" t="n">
         <v>265</v>
       </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="3" t="n">
+      <c r="G48" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="H48" s="4" t="n">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="D49" s="3" t="n">
         <v>45</v>
       </c>
-      <c r="B48" s="4" t="n">
+      <c r="E49" s="4" t="n">
         <v>270</v>
       </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="3" t="n">
+      <c r="G49" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="H49" s="4" t="n">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="D50" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="B49" s="4" t="n">
+      <c r="E50" s="4" t="n">
         <v>275</v>
       </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="3" t="n">
+      <c r="G50" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="H50" s="4" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="D51" s="3" t="n">
         <v>47</v>
       </c>
-      <c r="B50" s="4" t="n">
+      <c r="E51" s="4" t="n">
         <v>280</v>
       </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="3" t="n">
+      <c r="G51" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="H51" s="4" t="n">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="D52" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="B51" s="4" t="n">
+      <c r="E52" s="4" t="n">
         <v>285</v>
       </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="3" t="n">
+      <c r="G52" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="H52" s="4" t="n">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="D53" s="3" t="n">
         <v>49</v>
       </c>
-      <c r="B52" s="4" t="n">
+      <c r="E53" s="4" t="n">
         <v>290</v>
       </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="n">
+      <c r="G53" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="H53" s="4" t="n">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="D54" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="B53" s="4" t="n">
+      <c r="E54" s="4" t="n">
         <v>295</v>
       </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="n">
+      <c r="G54" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="H54" s="4" t="n">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="D55" s="3" t="n">
         <v>51</v>
       </c>
-      <c r="B54" s="4" t="n">
+      <c r="E55" s="4" t="n">
         <v>300</v>
       </c>
+      <c r="G55" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="H55" s="4" t="n">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="G56" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="H56" s="4" t="n">
+        <v>280</v>
+      </c>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="inlineStr">
-        <is>
-          <t>Total: 51 sizes</t>
+      <c r="G57" s="3" t="n">
+        <v>53</v>
+      </c>
+      <c r="H57" s="4" t="n">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="G58" s="3" t="n">
+        <v>54</v>
+      </c>
+      <c r="H58" s="4" t="n">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>NOTE: Bearing Dia must always be LESS than Centre Dia</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Shaft Length: Manual entry by user</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="8" t="inlineStr">
+        <is>
+          <t>Yellow cells = Enter your rates</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2006,476 +2419,243 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B61"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SHAFT DIA @ BEARING (25-290mm, 5mm gaps)</t>
+          <t>END PLATE PRICING</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Sr. No.</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Shaft Dia @ Bearing (mm)</t>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Material: MS</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="4" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="4" t="n">
-        <v>30</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Diameter: Same as Pipe Dia</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>40</v>
-      </c>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>MS Rate (₹/kg):</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>45</v>
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>THICKNESSES (mm):</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>50</v>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Sr.</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Thickness (mm)</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B10" s="4" t="n">
-        <v>55</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" s="4" t="n">
         <v>8</v>
-      </c>
-      <c r="B11" s="4" t="n">
-        <v>60</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B12" s="4" t="n">
-        <v>65</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B13" s="4" t="n">
-        <v>70</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B14" s="4" t="n">
-        <v>75</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B15" s="4" t="n">
-        <v>80</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B16" s="4" t="n">
-        <v>85</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B17" s="4" t="n">
-        <v>90</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B18" s="4" t="n">
-        <v>95</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B19" s="4" t="n">
-        <v>100</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B20" s="4" t="n">
-        <v>105</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B21" s="4" t="n">
-        <v>110</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B22" s="4" t="n">
-        <v>115</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B23" s="4" t="n">
-        <v>120</v>
+        <v>32</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B24" s="4" t="n">
-        <v>125</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B25" s="4" t="n">
-        <v>130</v>
+        <v>36</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B26" s="4" t="n">
-        <v>135</v>
+        <v>38</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B27" s="4" t="n">
-        <v>140</v>
+        <v>40</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="B28" s="4" t="n">
-        <v>145</v>
+        <v>42</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B29" s="4" t="n">
-        <v>150</v>
+        <v>44</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B30" s="4" t="n">
-        <v>155</v>
+        <v>46</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B31" s="4" t="n">
-        <v>160</v>
+        <v>48</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B32" s="4" t="n">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="B33" s="4" t="n">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="n">
-        <v>31</v>
-      </c>
-      <c r="B34" s="4" t="n">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="B35" s="4" t="n">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="n">
-        <v>33</v>
-      </c>
-      <c r="B36" s="4" t="n">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="B37" s="4" t="n">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="B38" s="4" t="n">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="n">
-        <v>36</v>
-      </c>
-      <c r="B39" s="4" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="n">
-        <v>37</v>
-      </c>
-      <c r="B40" s="4" t="n">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="n">
-        <v>38</v>
-      </c>
-      <c r="B41" s="4" t="n">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="n">
-        <v>39</v>
-      </c>
-      <c r="B42" s="4" t="n">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="B43" s="4" t="n">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="3" t="n">
-        <v>41</v>
-      </c>
-      <c r="B44" s="4" t="n">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="B45" s="4" t="n">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="n">
-        <v>43</v>
-      </c>
-      <c r="B46" s="4" t="n">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="n">
-        <v>44</v>
-      </c>
-      <c r="B47" s="4" t="n">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="3" t="n">
-        <v>45</v>
-      </c>
-      <c r="B48" s="4" t="n">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="3" t="n">
-        <v>46</v>
-      </c>
-      <c r="B49" s="4" t="n">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="3" t="n">
-        <v>47</v>
-      </c>
-      <c r="B50" s="4" t="n">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="3" t="n">
-        <v>48</v>
-      </c>
-      <c r="B51" s="4" t="n">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="3" t="n">
-        <v>49</v>
-      </c>
-      <c r="B52" s="4" t="n">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="n">
         <v>50</v>
-      </c>
-      <c r="B53" s="4" t="n">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="n">
-        <v>51</v>
-      </c>
-      <c r="B54" s="4" t="n">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="3" t="n">
-        <v>52</v>
-      </c>
-      <c r="B55" s="4" t="n">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="3" t="n">
-        <v>53</v>
-      </c>
-      <c r="B56" s="4" t="n">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="3" t="n">
-        <v>54</v>
-      </c>
-      <c r="B57" s="4" t="n">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="5" t="inlineStr">
-        <is>
-          <t>Total: 54 sizes</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="6" t="inlineStr">
-        <is>
-          <t>NOTE: Bearing Dia must always be LESS than Centre Dia</t>
-        </is>
       </c>
     </row>
   </sheetData>
@@ -2492,122 +2672,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:B47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>SHAFT MATERIAL RATES (₹/kg) - TO FILL</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Material Grade</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Rate (₹/kg)</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>MS (Mild Steel)</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr"/>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Standard mild steel</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>EN-8</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr"/>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Medium carbon steel</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>EN-9</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr"/>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>High carbon steel</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>EN-19</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="inlineStr"/>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Alloy steel - high strength</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>Yellow cells = Enter your rates</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B34"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>END PLATE PRICING - TO FILL</t>
+          <t>HUB PRICING</t>
         </is>
       </c>
     </row>
@@ -2621,7 +2696,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Diameter: Same as Pipe Dia</t>
+          <t>Options: No Hub / With Hub</t>
         </is>
       </c>
     </row>
@@ -2631,141 +2706,319 @@
           <t>MS Rate (₹/kg):</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr"/>
+      <c r="B6" s="6" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>THICKNESSES:</t>
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>HUB DIAMETERS (mm):</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Thickness (mm)</t>
+          <t>Sr.</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Hub Dia (mm)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="n">
+      <c r="A10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
         <v>6</v>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="n">
+      <c r="B15" s="4" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
         <v>8</v>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="n">
+      <c r="B17" s="4" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
         <v>10</v>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="n">
+      <c r="B19" s="4" t="n">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
         <v>12</v>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="n">
+      <c r="B21" s="4" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
         <v>14</v>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="n">
+      <c r="B23" s="4" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="B24" s="4" t="n">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
         <v>16</v>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="n">
+      <c r="B25" s="4" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="B26" s="4" t="n">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n">
         <v>18</v>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="n">
+      <c r="B27" s="4" t="n">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="B28" s="4" t="n">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n">
         <v>20</v>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="n">
+      <c r="B29" s="4" t="n">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B30" s="4" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n">
         <v>22</v>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="n">
+      <c r="B31" s="4" t="n">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="B32" s="4" t="n">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
         <v>24</v>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="n">
+      <c r="B33" s="4" t="n">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="B34" s="4" t="n">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
         <v>26</v>
       </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="n">
+      <c r="B35" s="4" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="B36" s="4" t="n">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n">
         <v>28</v>
       </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="n">
+      <c r="B37" s="4" t="n">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="B38" s="4" t="n">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="n">
         <v>30</v>
       </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="n">
+      <c r="B39" s="4" t="n">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="B40" s="4" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="n">
         <v>32</v>
       </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="n">
+      <c r="B41" s="4" t="n">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="B42" s="4" t="n">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="n">
         <v>34</v>
       </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="n">
+      <c r="B43" s="4" t="n">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="B44" s="4" t="n">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="n">
         <v>36</v>
       </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="n">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="n">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="n">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="n">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="n">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>Total: 23 thicknesses</t>
+      <c r="B45" s="4" t="n">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Hub Length: Manual entry</t>
         </is>
       </c>
     </row>
@@ -2777,378 +3030,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B48"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>HUB PRICING - TO FILL</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Material: MS</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Options: No Hub / With Hub</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>MS Rate (₹/kg):</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>HUB DIAMETERS:</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Sr. No.</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Hub Dia (mm)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B10" s="4" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B11" s="4" t="n">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B12" s="4" t="n">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="B13" s="4" t="n">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="B14" s="4" t="n">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="B15" s="4" t="n">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="B16" s="4" t="n">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="B17" s="4" t="n">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="B18" s="4" t="n">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="B19" s="4" t="n">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="B20" s="4" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="B21" s="4" t="n">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="B22" s="4" t="n">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="B23" s="4" t="n">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="B24" s="4" t="n">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="B25" s="4" t="n">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="B26" s="4" t="n">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="B27" s="4" t="n">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="B28" s="4" t="n">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="B29" s="4" t="n">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="B30" s="4" t="n">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="B31" s="4" t="n">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="B32" s="4" t="n">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="B33" s="4" t="n">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="B34" s="4" t="n">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="B35" s="4" t="n">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="n">
-        <v>27</v>
-      </c>
-      <c r="B36" s="4" t="n">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="B37" s="4" t="n">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="B38" s="4" t="n">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="B39" s="4" t="n">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="n">
-        <v>31</v>
-      </c>
-      <c r="B40" s="4" t="n">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="B41" s="4" t="n">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="n">
-        <v>33</v>
-      </c>
-      <c r="B42" s="4" t="n">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="B43" s="4" t="n">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="B44" s="4" t="n">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="n">
-        <v>36</v>
-      </c>
-      <c r="B45" s="4" t="n">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t>Total: 36 sizes</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Hub Length: Manual entry by user</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3193,124 +3075,124 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr"/>
-      <c r="B4" s="7" t="inlineStr"/>
-      <c r="C4" s="7" t="inlineStr"/>
-      <c r="D4" s="7" t="inlineStr"/>
+      <c r="A4" s="6" t="inlineStr"/>
+      <c r="B4" s="6" t="inlineStr"/>
+      <c r="C4" s="6" t="inlineStr"/>
+      <c r="D4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr"/>
-      <c r="B5" s="7" t="inlineStr"/>
-      <c r="C5" s="7" t="inlineStr"/>
-      <c r="D5" s="7" t="inlineStr"/>
+      <c r="A5" s="6" t="inlineStr"/>
+      <c r="B5" s="6" t="inlineStr"/>
+      <c r="C5" s="6" t="inlineStr"/>
+      <c r="D5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr"/>
-      <c r="B6" s="7" t="inlineStr"/>
-      <c r="C6" s="7" t="inlineStr"/>
-      <c r="D6" s="7" t="inlineStr"/>
+      <c r="A6" s="6" t="inlineStr"/>
+      <c r="B6" s="6" t="inlineStr"/>
+      <c r="C6" s="6" t="inlineStr"/>
+      <c r="D6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr"/>
-      <c r="B7" s="7" t="inlineStr"/>
-      <c r="C7" s="7" t="inlineStr"/>
-      <c r="D7" s="7" t="inlineStr"/>
+      <c r="A7" s="6" t="inlineStr"/>
+      <c r="B7" s="6" t="inlineStr"/>
+      <c r="C7" s="6" t="inlineStr"/>
+      <c r="D7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr"/>
-      <c r="B8" s="7" t="inlineStr"/>
-      <c r="C8" s="7" t="inlineStr"/>
-      <c r="D8" s="7" t="inlineStr"/>
+      <c r="A8" s="6" t="inlineStr"/>
+      <c r="B8" s="6" t="inlineStr"/>
+      <c r="C8" s="6" t="inlineStr"/>
+      <c r="D8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr"/>
-      <c r="B9" s="7" t="inlineStr"/>
-      <c r="C9" s="7" t="inlineStr"/>
-      <c r="D9" s="7" t="inlineStr"/>
+      <c r="A9" s="6" t="inlineStr"/>
+      <c r="B9" s="6" t="inlineStr"/>
+      <c r="C9" s="6" t="inlineStr"/>
+      <c r="D9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr"/>
-      <c r="B10" s="7" t="inlineStr"/>
-      <c r="C10" s="7" t="inlineStr"/>
-      <c r="D10" s="7" t="inlineStr"/>
+      <c r="A10" s="6" t="inlineStr"/>
+      <c r="B10" s="6" t="inlineStr"/>
+      <c r="C10" s="6" t="inlineStr"/>
+      <c r="D10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr"/>
-      <c r="B11" s="7" t="inlineStr"/>
-      <c r="C11" s="7" t="inlineStr"/>
-      <c r="D11" s="7" t="inlineStr"/>
+      <c r="A11" s="6" t="inlineStr"/>
+      <c r="B11" s="6" t="inlineStr"/>
+      <c r="C11" s="6" t="inlineStr"/>
+      <c r="D11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr"/>
-      <c r="B12" s="7" t="inlineStr"/>
-      <c r="C12" s="7" t="inlineStr"/>
-      <c r="D12" s="7" t="inlineStr"/>
+      <c r="A12" s="6" t="inlineStr"/>
+      <c r="B12" s="6" t="inlineStr"/>
+      <c r="C12" s="6" t="inlineStr"/>
+      <c r="D12" s="6" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr"/>
-      <c r="B13" s="7" t="inlineStr"/>
-      <c r="C13" s="7" t="inlineStr"/>
-      <c r="D13" s="7" t="inlineStr"/>
+      <c r="A13" s="6" t="inlineStr"/>
+      <c r="B13" s="6" t="inlineStr"/>
+      <c r="C13" s="6" t="inlineStr"/>
+      <c r="D13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr"/>
-      <c r="B14" s="7" t="inlineStr"/>
-      <c r="C14" s="7" t="inlineStr"/>
-      <c r="D14" s="7" t="inlineStr"/>
+      <c r="A14" s="6" t="inlineStr"/>
+      <c r="B14" s="6" t="inlineStr"/>
+      <c r="C14" s="6" t="inlineStr"/>
+      <c r="D14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr"/>
-      <c r="B15" s="7" t="inlineStr"/>
-      <c r="C15" s="7" t="inlineStr"/>
-      <c r="D15" s="7" t="inlineStr"/>
+      <c r="A15" s="6" t="inlineStr"/>
+      <c r="B15" s="6" t="inlineStr"/>
+      <c r="C15" s="6" t="inlineStr"/>
+      <c r="D15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr"/>
-      <c r="B16" s="7" t="inlineStr"/>
-      <c r="C16" s="7" t="inlineStr"/>
-      <c r="D16" s="7" t="inlineStr"/>
+      <c r="A16" s="6" t="inlineStr"/>
+      <c r="B16" s="6" t="inlineStr"/>
+      <c r="C16" s="6" t="inlineStr"/>
+      <c r="D16" s="6" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr"/>
-      <c r="B17" s="7" t="inlineStr"/>
-      <c r="C17" s="7" t="inlineStr"/>
-      <c r="D17" s="7" t="inlineStr"/>
+      <c r="A17" s="6" t="inlineStr"/>
+      <c r="B17" s="6" t="inlineStr"/>
+      <c r="C17" s="6" t="inlineStr"/>
+      <c r="D17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr"/>
-      <c r="B18" s="7" t="inlineStr"/>
-      <c r="C18" s="7" t="inlineStr"/>
-      <c r="D18" s="7" t="inlineStr"/>
+      <c r="A18" s="6" t="inlineStr"/>
+      <c r="B18" s="6" t="inlineStr"/>
+      <c r="C18" s="6" t="inlineStr"/>
+      <c r="D18" s="6" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr"/>
-      <c r="B19" s="7" t="inlineStr"/>
-      <c r="C19" s="7" t="inlineStr"/>
-      <c r="D19" s="7" t="inlineStr"/>
+      <c r="A19" s="6" t="inlineStr"/>
+      <c r="B19" s="6" t="inlineStr"/>
+      <c r="C19" s="6" t="inlineStr"/>
+      <c r="D19" s="6" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr"/>
-      <c r="B20" s="7" t="inlineStr"/>
-      <c r="C20" s="7" t="inlineStr"/>
-      <c r="D20" s="7" t="inlineStr"/>
+      <c r="A20" s="6" t="inlineStr"/>
+      <c r="B20" s="6" t="inlineStr"/>
+      <c r="C20" s="6" t="inlineStr"/>
+      <c r="D20" s="6" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr"/>
-      <c r="B21" s="7" t="inlineStr"/>
-      <c r="C21" s="7" t="inlineStr"/>
-      <c r="D21" s="7" t="inlineStr"/>
+      <c r="A21" s="6" t="inlineStr"/>
+      <c r="B21" s="6" t="inlineStr"/>
+      <c r="C21" s="6" t="inlineStr"/>
+      <c r="D21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="inlineStr"/>
-      <c r="B22" s="7" t="inlineStr"/>
-      <c r="C22" s="7" t="inlineStr"/>
-      <c r="D22" s="7" t="inlineStr"/>
+      <c r="A22" s="6" t="inlineStr"/>
+      <c r="B22" s="6" t="inlineStr"/>
+      <c r="C22" s="6" t="inlineStr"/>
+      <c r="D22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="inlineStr"/>
-      <c r="B23" s="7" t="inlineStr"/>
-      <c r="C23" s="7" t="inlineStr"/>
-      <c r="D23" s="7" t="inlineStr"/>
+      <c r="A23" s="6" t="inlineStr"/>
+      <c r="B23" s="6" t="inlineStr"/>
+      <c r="C23" s="6" t="inlineStr"/>
+      <c r="D23" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3320,7 +3202,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3336,12 +3218,12 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RUBBER LAGGING PRICING (₹/sqm) - TO FILL</t>
+          <t>RUBBER LAGGING PRICING (₹/sqm)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>PLAIN / DIAMOND (Same rates)</t>
         </is>
@@ -3363,46 +3245,46 @@
       <c r="A5" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B5" s="7" t="inlineStr"/>
+      <c r="B5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B6" s="7" t="inlineStr"/>
+      <c r="B6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B7" s="7" t="inlineStr"/>
+      <c r="B7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B8" s="7" t="inlineStr"/>
+      <c r="B8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B9" s="7" t="inlineStr"/>
+      <c r="B9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="B10" s="7" t="inlineStr"/>
+      <c r="B10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="B11" s="7" t="inlineStr"/>
+      <c r="B11" s="6" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>CERAMIC</t>
         </is>
@@ -3424,19 +3306,19 @@
       <c r="A16" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="7" t="inlineStr"/>
+      <c r="B16" s="6" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B17" s="7" t="inlineStr"/>
+      <c r="B17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="B18" s="7" t="inlineStr"/>
+      <c r="B18" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/backend/static/pulley_pricing_template.xlsx
+++ b/backend/static/pulley_pricing_template.xlsx
@@ -9,10 +9,11 @@
   <sheets>
     <sheet name="1. Pipe Pricing" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="2. Shaft Pricing" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="3. End Plate" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="4. Hub Pricing" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="5. KLA (LATER)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="6. Rubber Lagging" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="3. Shaft Dia @ Bearing" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="4. End Plate" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="5. Hub Pricing" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="6. KLA (LATER)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="7. Rubber Lagging" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,17 +43,13 @@
     </font>
     <font>
       <b val="1"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FF0000"/>
     </font>
     <font>
       <color rgb="00996600"/>
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00FF0000"/>
     </font>
   </fonts>
   <fills count="5">
@@ -99,7 +96,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -113,13 +110,12 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1553,867 +1549,1025 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H63"/>
+  <dimension ref="A1:E60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="3" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="3" customWidth="1" min="6" max="6"/>
-    <col width="6" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SHAFT SPECIFICATIONS &amp; PRICING</t>
+          <t>SHAFT PRICING - RATE PER KG (₹/kg) - Shaft Dia × Material</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>MATERIAL RATES (₹/kg)</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>SHAFT DIA @ CENTRE (mm)</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>SHAFT DIA @ BEARING (mm)</t>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Shaft Dia (mm)</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>EN-8</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>EN-9</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>EN-19</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Material Grade</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Rate (₹/kg)</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Sr.</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Dia (mm)</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Sr.</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Dia (mm)</t>
-        </is>
-      </c>
+      <c r="A4" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="B4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="inlineStr"/>
+      <c r="D4" s="5" t="inlineStr"/>
+      <c r="E4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>MS (Mild Steel)</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr"/>
-      <c r="D5" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" s="4" t="n">
-        <v>25</v>
-      </c>
+      <c r="A5" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="B5" s="5" t="inlineStr"/>
+      <c r="C5" s="5" t="inlineStr"/>
+      <c r="D5" s="5" t="inlineStr"/>
+      <c r="E5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>EN-8</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr"/>
-      <c r="D6" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>55</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="H6" s="4" t="n">
-        <v>30</v>
-      </c>
+      <c r="A6" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="B6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>EN-9</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr"/>
-      <c r="D7" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="H7" s="4" t="n">
-        <v>35</v>
-      </c>
+      <c r="A7" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr"/>
+      <c r="C7" s="5" t="inlineStr"/>
+      <c r="D7" s="5" t="inlineStr"/>
+      <c r="E7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>EN-19</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr"/>
-      <c r="D8" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>65</v>
-      </c>
-      <c r="G8" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="H8" s="4" t="n">
-        <v>40</v>
-      </c>
+      <c r="A8" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="B8" s="5" t="inlineStr"/>
+      <c r="C8" s="5" t="inlineStr"/>
+      <c r="D8" s="5" t="inlineStr"/>
+      <c r="E8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="D9" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>70</v>
-      </c>
-      <c r="G9" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="H9" s="4" t="n">
-        <v>45</v>
-      </c>
+      <c r="A9" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr"/>
+      <c r="C9" s="5" t="inlineStr"/>
+      <c r="D9" s="5" t="inlineStr"/>
+      <c r="E9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="D10" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>75</v>
-      </c>
-      <c r="G10" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="H10" s="4" t="n">
-        <v>50</v>
-      </c>
+      <c r="A10" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="inlineStr"/>
+      <c r="D10" s="5" t="inlineStr"/>
+      <c r="E10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="D11" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>80</v>
-      </c>
-      <c r="G11" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="H11" s="4" t="n">
-        <v>55</v>
-      </c>
+      <c r="A11" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="inlineStr"/>
+      <c r="D11" s="5" t="inlineStr"/>
+      <c r="E11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="D12" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>85</v>
-      </c>
-      <c r="G12" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="H12" s="4" t="n">
-        <v>60</v>
-      </c>
+      <c r="A12" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="inlineStr"/>
+      <c r="D12" s="5" t="inlineStr"/>
+      <c r="E12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="D13" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>90</v>
-      </c>
-      <c r="G13" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="H13" s="4" t="n">
-        <v>65</v>
-      </c>
+      <c r="A13" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr"/>
+      <c r="C13" s="5" t="inlineStr"/>
+      <c r="D13" s="5" t="inlineStr"/>
+      <c r="E13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="D14" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>95</v>
-      </c>
-      <c r="G14" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="H14" s="4" t="n">
-        <v>70</v>
-      </c>
+      <c r="A14" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B14" s="5" t="inlineStr"/>
+      <c r="C14" s="5" t="inlineStr"/>
+      <c r="D14" s="5" t="inlineStr"/>
+      <c r="E14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="D15" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="G15" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="H15" s="4" t="n">
-        <v>75</v>
-      </c>
+      <c r="A15" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr"/>
+      <c r="C15" s="5" t="inlineStr"/>
+      <c r="D15" s="5" t="inlineStr"/>
+      <c r="E15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="D16" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="E16" s="4" t="n">
-        <v>105</v>
-      </c>
-      <c r="G16" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="H16" s="4" t="n">
-        <v>80</v>
-      </c>
+      <c r="A16" s="3" t="n">
+        <v>110</v>
+      </c>
+      <c r="B16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="inlineStr"/>
+      <c r="D16" s="5" t="inlineStr"/>
+      <c r="E16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="D17" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="E17" s="4" t="n">
-        <v>110</v>
-      </c>
-      <c r="G17" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="H17" s="4" t="n">
-        <v>85</v>
-      </c>
+      <c r="A17" s="3" t="n">
+        <v>115</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="inlineStr"/>
+      <c r="D17" s="5" t="inlineStr"/>
+      <c r="E17" s="5" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="D18" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="E18" s="4" t="n">
-        <v>115</v>
-      </c>
-      <c r="G18" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="H18" s="4" t="n">
-        <v>90</v>
-      </c>
+      <c r="A18" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="B18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="inlineStr"/>
+      <c r="D18" s="5" t="inlineStr"/>
+      <c r="E18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="D19" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>120</v>
-      </c>
-      <c r="G19" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="H19" s="4" t="n">
-        <v>95</v>
-      </c>
+      <c r="A19" s="3" t="n">
+        <v>125</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr"/>
+      <c r="C19" s="5" t="inlineStr"/>
+      <c r="D19" s="5" t="inlineStr"/>
+      <c r="E19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="D20" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="E20" s="4" t="n">
-        <v>125</v>
-      </c>
-      <c r="G20" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="H20" s="4" t="n">
-        <v>100</v>
-      </c>
+      <c r="A20" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="B20" s="5" t="inlineStr"/>
+      <c r="C20" s="5" t="inlineStr"/>
+      <c r="D20" s="5" t="inlineStr"/>
+      <c r="E20" s="5" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="D21" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="E21" s="4" t="n">
-        <v>130</v>
-      </c>
-      <c r="G21" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="H21" s="4" t="n">
-        <v>105</v>
-      </c>
+      <c r="A21" s="3" t="n">
+        <v>135</v>
+      </c>
+      <c r="B21" s="5" t="inlineStr"/>
+      <c r="C21" s="5" t="inlineStr"/>
+      <c r="D21" s="5" t="inlineStr"/>
+      <c r="E21" s="5" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="D22" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="E22" s="4" t="n">
-        <v>135</v>
-      </c>
-      <c r="G22" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="H22" s="4" t="n">
-        <v>110</v>
-      </c>
+      <c r="A22" s="3" t="n">
+        <v>140</v>
+      </c>
+      <c r="B22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="inlineStr"/>
+      <c r="D22" s="5" t="inlineStr"/>
+      <c r="E22" s="5" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="D23" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="E23" s="4" t="n">
-        <v>140</v>
-      </c>
-      <c r="G23" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="H23" s="4" t="n">
-        <v>115</v>
-      </c>
+      <c r="A23" s="3" t="n">
+        <v>145</v>
+      </c>
+      <c r="B23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="inlineStr"/>
+      <c r="D23" s="5" t="inlineStr"/>
+      <c r="E23" s="5" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="D24" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="E24" s="4" t="n">
-        <v>145</v>
-      </c>
-      <c r="G24" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="H24" s="4" t="n">
-        <v>120</v>
-      </c>
+      <c r="A24" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="B24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="inlineStr"/>
+      <c r="D24" s="5" t="inlineStr"/>
+      <c r="E24" s="5" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="D25" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="E25" s="4" t="n">
-        <v>150</v>
-      </c>
-      <c r="G25" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="H25" s="4" t="n">
-        <v>125</v>
-      </c>
+      <c r="A25" s="3" t="n">
+        <v>155</v>
+      </c>
+      <c r="B25" s="5" t="inlineStr"/>
+      <c r="C25" s="5" t="inlineStr"/>
+      <c r="D25" s="5" t="inlineStr"/>
+      <c r="E25" s="5" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="D26" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="E26" s="4" t="n">
-        <v>155</v>
-      </c>
-      <c r="G26" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="H26" s="4" t="n">
-        <v>130</v>
-      </c>
+      <c r="A26" s="3" t="n">
+        <v>160</v>
+      </c>
+      <c r="B26" s="5" t="inlineStr"/>
+      <c r="C26" s="5" t="inlineStr"/>
+      <c r="D26" s="5" t="inlineStr"/>
+      <c r="E26" s="5" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="D27" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="E27" s="4" t="n">
-        <v>160</v>
-      </c>
-      <c r="G27" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="H27" s="4" t="n">
-        <v>135</v>
-      </c>
+      <c r="A27" s="3" t="n">
+        <v>165</v>
+      </c>
+      <c r="B27" s="5" t="inlineStr"/>
+      <c r="C27" s="5" t="inlineStr"/>
+      <c r="D27" s="5" t="inlineStr"/>
+      <c r="E27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="D28" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="E28" s="4" t="n">
-        <v>165</v>
-      </c>
-      <c r="G28" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="H28" s="4" t="n">
-        <v>140</v>
-      </c>
+      <c r="A28" s="3" t="n">
+        <v>170</v>
+      </c>
+      <c r="B28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="inlineStr"/>
+      <c r="D28" s="5" t="inlineStr"/>
+      <c r="E28" s="5" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="D29" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="E29" s="4" t="n">
-        <v>170</v>
-      </c>
-      <c r="G29" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="H29" s="4" t="n">
-        <v>145</v>
-      </c>
+      <c r="A29" s="3" t="n">
+        <v>175</v>
+      </c>
+      <c r="B29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="inlineStr"/>
+      <c r="D29" s="5" t="inlineStr"/>
+      <c r="E29" s="5" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="D30" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="E30" s="4" t="n">
-        <v>175</v>
-      </c>
-      <c r="G30" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="H30" s="4" t="n">
-        <v>150</v>
-      </c>
+      <c r="A30" s="3" t="n">
+        <v>180</v>
+      </c>
+      <c r="B30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="inlineStr"/>
+      <c r="D30" s="5" t="inlineStr"/>
+      <c r="E30" s="5" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="D31" s="3" t="n">
-        <v>27</v>
-      </c>
-      <c r="E31" s="4" t="n">
-        <v>180</v>
-      </c>
-      <c r="G31" s="3" t="n">
-        <v>27</v>
-      </c>
-      <c r="H31" s="4" t="n">
-        <v>155</v>
-      </c>
+      <c r="A31" s="3" t="n">
+        <v>185</v>
+      </c>
+      <c r="B31" s="5" t="inlineStr"/>
+      <c r="C31" s="5" t="inlineStr"/>
+      <c r="D31" s="5" t="inlineStr"/>
+      <c r="E31" s="5" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="D32" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="E32" s="4" t="n">
-        <v>185</v>
-      </c>
-      <c r="G32" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="H32" s="4" t="n">
-        <v>160</v>
-      </c>
+      <c r="A32" s="3" t="n">
+        <v>190</v>
+      </c>
+      <c r="B32" s="5" t="inlineStr"/>
+      <c r="C32" s="5" t="inlineStr"/>
+      <c r="D32" s="5" t="inlineStr"/>
+      <c r="E32" s="5" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="D33" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="E33" s="4" t="n">
-        <v>190</v>
-      </c>
-      <c r="G33" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="H33" s="4" t="n">
-        <v>165</v>
-      </c>
+      <c r="A33" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="B33" s="5" t="inlineStr"/>
+      <c r="C33" s="5" t="inlineStr"/>
+      <c r="D33" s="5" t="inlineStr"/>
+      <c r="E33" s="5" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="D34" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="E34" s="4" t="n">
-        <v>195</v>
-      </c>
-      <c r="G34" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="H34" s="4" t="n">
-        <v>170</v>
-      </c>
+      <c r="A34" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="B34" s="5" t="inlineStr"/>
+      <c r="C34" s="5" t="inlineStr"/>
+      <c r="D34" s="5" t="inlineStr"/>
+      <c r="E34" s="5" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="D35" s="3" t="n">
-        <v>31</v>
-      </c>
-      <c r="E35" s="4" t="n">
-        <v>200</v>
-      </c>
-      <c r="G35" s="3" t="n">
-        <v>31</v>
-      </c>
-      <c r="H35" s="4" t="n">
-        <v>175</v>
-      </c>
+      <c r="A35" s="3" t="n">
+        <v>205</v>
+      </c>
+      <c r="B35" s="5" t="inlineStr"/>
+      <c r="C35" s="5" t="inlineStr"/>
+      <c r="D35" s="5" t="inlineStr"/>
+      <c r="E35" s="5" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="D36" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="E36" s="4" t="n">
-        <v>205</v>
-      </c>
-      <c r="G36" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="H36" s="4" t="n">
-        <v>180</v>
-      </c>
+      <c r="A36" s="3" t="n">
+        <v>210</v>
+      </c>
+      <c r="B36" s="5" t="inlineStr"/>
+      <c r="C36" s="5" t="inlineStr"/>
+      <c r="D36" s="5" t="inlineStr"/>
+      <c r="E36" s="5" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="D37" s="3" t="n">
-        <v>33</v>
-      </c>
-      <c r="E37" s="4" t="n">
-        <v>210</v>
-      </c>
-      <c r="G37" s="3" t="n">
-        <v>33</v>
-      </c>
-      <c r="H37" s="4" t="n">
-        <v>185</v>
-      </c>
+      <c r="A37" s="3" t="n">
+        <v>215</v>
+      </c>
+      <c r="B37" s="5" t="inlineStr"/>
+      <c r="C37" s="5" t="inlineStr"/>
+      <c r="D37" s="5" t="inlineStr"/>
+      <c r="E37" s="5" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="D38" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="E38" s="4" t="n">
-        <v>215</v>
-      </c>
-      <c r="G38" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="H38" s="4" t="n">
-        <v>190</v>
-      </c>
+      <c r="A38" s="3" t="n">
+        <v>220</v>
+      </c>
+      <c r="B38" s="5" t="inlineStr"/>
+      <c r="C38" s="5" t="inlineStr"/>
+      <c r="D38" s="5" t="inlineStr"/>
+      <c r="E38" s="5" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="D39" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="E39" s="4" t="n">
-        <v>220</v>
-      </c>
-      <c r="G39" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="H39" s="4" t="n">
-        <v>195</v>
-      </c>
+      <c r="A39" s="3" t="n">
+        <v>225</v>
+      </c>
+      <c r="B39" s="5" t="inlineStr"/>
+      <c r="C39" s="5" t="inlineStr"/>
+      <c r="D39" s="5" t="inlineStr"/>
+      <c r="E39" s="5" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="D40" s="3" t="n">
-        <v>36</v>
-      </c>
-      <c r="E40" s="4" t="n">
-        <v>225</v>
-      </c>
-      <c r="G40" s="3" t="n">
-        <v>36</v>
-      </c>
-      <c r="H40" s="4" t="n">
-        <v>200</v>
-      </c>
+      <c r="A40" s="3" t="n">
+        <v>230</v>
+      </c>
+      <c r="B40" s="5" t="inlineStr"/>
+      <c r="C40" s="5" t="inlineStr"/>
+      <c r="D40" s="5" t="inlineStr"/>
+      <c r="E40" s="5" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="D41" s="3" t="n">
-        <v>37</v>
-      </c>
-      <c r="E41" s="4" t="n">
-        <v>230</v>
-      </c>
-      <c r="G41" s="3" t="n">
-        <v>37</v>
-      </c>
-      <c r="H41" s="4" t="n">
-        <v>205</v>
-      </c>
+      <c r="A41" s="3" t="n">
+        <v>235</v>
+      </c>
+      <c r="B41" s="5" t="inlineStr"/>
+      <c r="C41" s="5" t="inlineStr"/>
+      <c r="D41" s="5" t="inlineStr"/>
+      <c r="E41" s="5" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="D42" s="3" t="n">
-        <v>38</v>
-      </c>
-      <c r="E42" s="4" t="n">
-        <v>235</v>
-      </c>
-      <c r="G42" s="3" t="n">
-        <v>38</v>
-      </c>
-      <c r="H42" s="4" t="n">
-        <v>210</v>
-      </c>
+      <c r="A42" s="3" t="n">
+        <v>240</v>
+      </c>
+      <c r="B42" s="5" t="inlineStr"/>
+      <c r="C42" s="5" t="inlineStr"/>
+      <c r="D42" s="5" t="inlineStr"/>
+      <c r="E42" s="5" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="D43" s="3" t="n">
-        <v>39</v>
-      </c>
-      <c r="E43" s="4" t="n">
-        <v>240</v>
-      </c>
-      <c r="G43" s="3" t="n">
-        <v>39</v>
-      </c>
-      <c r="H43" s="4" t="n">
-        <v>215</v>
-      </c>
+      <c r="A43" s="3" t="n">
+        <v>245</v>
+      </c>
+      <c r="B43" s="5" t="inlineStr"/>
+      <c r="C43" s="5" t="inlineStr"/>
+      <c r="D43" s="5" t="inlineStr"/>
+      <c r="E43" s="5" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="D44" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="E44" s="4" t="n">
-        <v>245</v>
-      </c>
-      <c r="G44" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="H44" s="4" t="n">
-        <v>220</v>
-      </c>
+      <c r="A44" s="3" t="n">
+        <v>250</v>
+      </c>
+      <c r="B44" s="5" t="inlineStr"/>
+      <c r="C44" s="5" t="inlineStr"/>
+      <c r="D44" s="5" t="inlineStr"/>
+      <c r="E44" s="5" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="D45" s="3" t="n">
-        <v>41</v>
-      </c>
-      <c r="E45" s="4" t="n">
-        <v>250</v>
-      </c>
-      <c r="G45" s="3" t="n">
-        <v>41</v>
-      </c>
-      <c r="H45" s="4" t="n">
-        <v>225</v>
-      </c>
+      <c r="A45" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="B45" s="5" t="inlineStr"/>
+      <c r="C45" s="5" t="inlineStr"/>
+      <c r="D45" s="5" t="inlineStr"/>
+      <c r="E45" s="5" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="D46" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="E46" s="4" t="n">
-        <v>255</v>
-      </c>
-      <c r="G46" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="H46" s="4" t="n">
-        <v>230</v>
-      </c>
+      <c r="A46" s="3" t="n">
+        <v>260</v>
+      </c>
+      <c r="B46" s="5" t="inlineStr"/>
+      <c r="C46" s="5" t="inlineStr"/>
+      <c r="D46" s="5" t="inlineStr"/>
+      <c r="E46" s="5" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="D47" s="3" t="n">
-        <v>43</v>
-      </c>
-      <c r="E47" s="4" t="n">
-        <v>260</v>
-      </c>
-      <c r="G47" s="3" t="n">
-        <v>43</v>
-      </c>
-      <c r="H47" s="4" t="n">
-        <v>235</v>
-      </c>
+      <c r="A47" s="3" t="n">
+        <v>265</v>
+      </c>
+      <c r="B47" s="5" t="inlineStr"/>
+      <c r="C47" s="5" t="inlineStr"/>
+      <c r="D47" s="5" t="inlineStr"/>
+      <c r="E47" s="5" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="D48" s="3" t="n">
-        <v>44</v>
-      </c>
-      <c r="E48" s="4" t="n">
-        <v>265</v>
-      </c>
-      <c r="G48" s="3" t="n">
-        <v>44</v>
-      </c>
-      <c r="H48" s="4" t="n">
-        <v>240</v>
-      </c>
+      <c r="A48" s="3" t="n">
+        <v>270</v>
+      </c>
+      <c r="B48" s="5" t="inlineStr"/>
+      <c r="C48" s="5" t="inlineStr"/>
+      <c r="D48" s="5" t="inlineStr"/>
+      <c r="E48" s="5" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="D49" s="3" t="n">
-        <v>45</v>
-      </c>
-      <c r="E49" s="4" t="n">
-        <v>270</v>
-      </c>
-      <c r="G49" s="3" t="n">
-        <v>45</v>
-      </c>
-      <c r="H49" s="4" t="n">
-        <v>245</v>
-      </c>
+      <c r="A49" s="3" t="n">
+        <v>275</v>
+      </c>
+      <c r="B49" s="5" t="inlineStr"/>
+      <c r="C49" s="5" t="inlineStr"/>
+      <c r="D49" s="5" t="inlineStr"/>
+      <c r="E49" s="5" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="D50" s="3" t="n">
-        <v>46</v>
-      </c>
-      <c r="E50" s="4" t="n">
-        <v>275</v>
-      </c>
-      <c r="G50" s="3" t="n">
-        <v>46</v>
-      </c>
-      <c r="H50" s="4" t="n">
-        <v>250</v>
-      </c>
+      <c r="A50" s="3" t="n">
+        <v>280</v>
+      </c>
+      <c r="B50" s="5" t="inlineStr"/>
+      <c r="C50" s="5" t="inlineStr"/>
+      <c r="D50" s="5" t="inlineStr"/>
+      <c r="E50" s="5" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="D51" s="3" t="n">
-        <v>47</v>
-      </c>
-      <c r="E51" s="4" t="n">
-        <v>280</v>
-      </c>
-      <c r="G51" s="3" t="n">
-        <v>47</v>
-      </c>
-      <c r="H51" s="4" t="n">
-        <v>255</v>
-      </c>
+      <c r="A51" s="3" t="n">
+        <v>285</v>
+      </c>
+      <c r="B51" s="5" t="inlineStr"/>
+      <c r="C51" s="5" t="inlineStr"/>
+      <c r="D51" s="5" t="inlineStr"/>
+      <c r="E51" s="5" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="D52" s="3" t="n">
-        <v>48</v>
-      </c>
-      <c r="E52" s="4" t="n">
-        <v>285</v>
-      </c>
-      <c r="G52" s="3" t="n">
-        <v>48</v>
-      </c>
-      <c r="H52" s="4" t="n">
-        <v>260</v>
-      </c>
+      <c r="A52" s="3" t="n">
+        <v>290</v>
+      </c>
+      <c r="B52" s="5" t="inlineStr"/>
+      <c r="C52" s="5" t="inlineStr"/>
+      <c r="D52" s="5" t="inlineStr"/>
+      <c r="E52" s="5" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="D53" s="3" t="n">
-        <v>49</v>
-      </c>
-      <c r="E53" s="4" t="n">
-        <v>290</v>
-      </c>
-      <c r="G53" s="3" t="n">
-        <v>49</v>
-      </c>
-      <c r="H53" s="4" t="n">
-        <v>265</v>
-      </c>
+      <c r="A53" s="3" t="n">
+        <v>295</v>
+      </c>
+      <c r="B53" s="5" t="inlineStr"/>
+      <c r="C53" s="5" t="inlineStr"/>
+      <c r="D53" s="5" t="inlineStr"/>
+      <c r="E53" s="5" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="D54" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="E54" s="4" t="n">
-        <v>295</v>
-      </c>
-      <c r="G54" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="H54" s="4" t="n">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="D55" s="3" t="n">
-        <v>51</v>
-      </c>
-      <c r="E55" s="4" t="n">
+      <c r="A54" s="3" t="n">
         <v>300</v>
       </c>
-      <c r="G55" s="3" t="n">
-        <v>51</v>
-      </c>
-      <c r="H55" s="4" t="n">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="G56" s="3" t="n">
-        <v>52</v>
-      </c>
-      <c r="H56" s="4" t="n">
-        <v>280</v>
-      </c>
+      <c r="B54" s="5" t="inlineStr"/>
+      <c r="C54" s="5" t="inlineStr"/>
+      <c r="D54" s="5" t="inlineStr"/>
+      <c r="E54" s="5" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="G57" s="3" t="n">
-        <v>53</v>
-      </c>
-      <c r="H57" s="4" t="n">
-        <v>285</v>
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>Total: 51 shaft diameters × 4 materials = 204 combinations</t>
+        </is>
       </c>
     </row>
     <row r="58">
-      <c r="G58" s="3" t="n">
-        <v>54</v>
-      </c>
-      <c r="H58" s="4" t="n">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="7" t="inlineStr">
-        <is>
-          <t>NOTE: Bearing Dia must always be LESS than Centre Dia</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Shaft Length: Manual entry by user</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="8" t="inlineStr">
-        <is>
-          <t>Yellow cells = Enter your rates</t>
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>Yellow cells = Enter rate (₹/kg) for each combination</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Shaft Length: Manual entry by user (not in this table)</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B61"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>SHAFT DIA @ BEARING (for reference)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>NOTE: Bearing Dia must always be LESS than Centre Dia</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Sr.</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Shaft Dia @ Bearing (mm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B23" s="4" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="B24" s="4" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B25" s="4" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B26" s="4" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B27" s="4" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="B28" s="4" t="n">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="B29" s="4" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="B30" s="4" t="n">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="B31" s="4" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="B32" s="4" t="n">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="B33" s="4" t="n">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="B34" s="4" t="n">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="B35" s="4" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="B36" s="4" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="B37" s="4" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="B38" s="4" t="n">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="B39" s="4" t="n">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="B40" s="4" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="B41" s="4" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="B42" s="4" t="n">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="B43" s="4" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="B44" s="4" t="n">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="B45" s="4" t="n">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="B46" s="4" t="n">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="B47" s="4" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="B48" s="4" t="n">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="B49" s="4" t="n">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="B50" s="4" t="n">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="B51" s="4" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="B52" s="4" t="n">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="B53" s="4" t="n">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="B54" s="4" t="n">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="B55" s="4" t="n">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="B56" s="4" t="n">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="B57" s="4" t="n">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="n">
+        <v>53</v>
+      </c>
+      <c r="B58" s="4" t="n">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="n">
+        <v>54</v>
+      </c>
+      <c r="B59" s="4" t="n">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Total: 54 sizes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2453,10 +2607,10 @@
           <t>MS Rate (₹/kg):</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr"/>
+      <c r="B6" s="5" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>THICKNESSES (mm):</t>
         </is>
@@ -2666,7 +2820,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2706,10 +2860,10 @@
           <t>MS Rate (₹/kg):</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr"/>
+      <c r="B6" s="5" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>HUB DIAMETERS (mm):</t>
         </is>
@@ -3030,7 +3184,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3075,124 +3229,124 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr"/>
-      <c r="B4" s="6" t="inlineStr"/>
-      <c r="C4" s="6" t="inlineStr"/>
-      <c r="D4" s="6" t="inlineStr"/>
+      <c r="A4" s="5" t="inlineStr"/>
+      <c r="B4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="inlineStr"/>
+      <c r="D4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr"/>
-      <c r="B5" s="6" t="inlineStr"/>
-      <c r="C5" s="6" t="inlineStr"/>
-      <c r="D5" s="6" t="inlineStr"/>
+      <c r="A5" s="5" t="inlineStr"/>
+      <c r="B5" s="5" t="inlineStr"/>
+      <c r="C5" s="5" t="inlineStr"/>
+      <c r="D5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr"/>
-      <c r="B6" s="6" t="inlineStr"/>
-      <c r="C6" s="6" t="inlineStr"/>
-      <c r="D6" s="6" t="inlineStr"/>
+      <c r="A6" s="5" t="inlineStr"/>
+      <c r="B6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr"/>
-      <c r="B7" s="6" t="inlineStr"/>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr"/>
+      <c r="A7" s="5" t="inlineStr"/>
+      <c r="B7" s="5" t="inlineStr"/>
+      <c r="C7" s="5" t="inlineStr"/>
+      <c r="D7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr"/>
-      <c r="B8" s="6" t="inlineStr"/>
-      <c r="C8" s="6" t="inlineStr"/>
-      <c r="D8" s="6" t="inlineStr"/>
+      <c r="A8" s="5" t="inlineStr"/>
+      <c r="B8" s="5" t="inlineStr"/>
+      <c r="C8" s="5" t="inlineStr"/>
+      <c r="D8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr"/>
-      <c r="B9" s="6" t="inlineStr"/>
-      <c r="C9" s="6" t="inlineStr"/>
-      <c r="D9" s="6" t="inlineStr"/>
+      <c r="A9" s="5" t="inlineStr"/>
+      <c r="B9" s="5" t="inlineStr"/>
+      <c r="C9" s="5" t="inlineStr"/>
+      <c r="D9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr"/>
-      <c r="B10" s="6" t="inlineStr"/>
-      <c r="C10" s="6" t="inlineStr"/>
-      <c r="D10" s="6" t="inlineStr"/>
+      <c r="A10" s="5" t="inlineStr"/>
+      <c r="B10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="inlineStr"/>
+      <c r="D10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr"/>
-      <c r="B11" s="6" t="inlineStr"/>
-      <c r="C11" s="6" t="inlineStr"/>
-      <c r="D11" s="6" t="inlineStr"/>
+      <c r="A11" s="5" t="inlineStr"/>
+      <c r="B11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="inlineStr"/>
+      <c r="D11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr"/>
-      <c r="B12" s="6" t="inlineStr"/>
-      <c r="C12" s="6" t="inlineStr"/>
-      <c r="D12" s="6" t="inlineStr"/>
+      <c r="A12" s="5" t="inlineStr"/>
+      <c r="B12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="inlineStr"/>
+      <c r="D12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr"/>
-      <c r="B13" s="6" t="inlineStr"/>
-      <c r="C13" s="6" t="inlineStr"/>
-      <c r="D13" s="6" t="inlineStr"/>
+      <c r="A13" s="5" t="inlineStr"/>
+      <c r="B13" s="5" t="inlineStr"/>
+      <c r="C13" s="5" t="inlineStr"/>
+      <c r="D13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr"/>
-      <c r="B14" s="6" t="inlineStr"/>
-      <c r="C14" s="6" t="inlineStr"/>
-      <c r="D14" s="6" t="inlineStr"/>
+      <c r="A14" s="5" t="inlineStr"/>
+      <c r="B14" s="5" t="inlineStr"/>
+      <c r="C14" s="5" t="inlineStr"/>
+      <c r="D14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr"/>
-      <c r="B15" s="6" t="inlineStr"/>
-      <c r="C15" s="6" t="inlineStr"/>
-      <c r="D15" s="6" t="inlineStr"/>
+      <c r="A15" s="5" t="inlineStr"/>
+      <c r="B15" s="5" t="inlineStr"/>
+      <c r="C15" s="5" t="inlineStr"/>
+      <c r="D15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr"/>
-      <c r="B16" s="6" t="inlineStr"/>
-      <c r="C16" s="6" t="inlineStr"/>
-      <c r="D16" s="6" t="inlineStr"/>
+      <c r="A16" s="5" t="inlineStr"/>
+      <c r="B16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="inlineStr"/>
+      <c r="D16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr"/>
-      <c r="B17" s="6" t="inlineStr"/>
-      <c r="C17" s="6" t="inlineStr"/>
-      <c r="D17" s="6" t="inlineStr"/>
+      <c r="A17" s="5" t="inlineStr"/>
+      <c r="B17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="inlineStr"/>
+      <c r="D17" s="5" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr"/>
-      <c r="B18" s="6" t="inlineStr"/>
-      <c r="C18" s="6" t="inlineStr"/>
-      <c r="D18" s="6" t="inlineStr"/>
+      <c r="A18" s="5" t="inlineStr"/>
+      <c r="B18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="inlineStr"/>
+      <c r="D18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr"/>
-      <c r="B19" s="6" t="inlineStr"/>
-      <c r="C19" s="6" t="inlineStr"/>
-      <c r="D19" s="6" t="inlineStr"/>
+      <c r="A19" s="5" t="inlineStr"/>
+      <c r="B19" s="5" t="inlineStr"/>
+      <c r="C19" s="5" t="inlineStr"/>
+      <c r="D19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr"/>
-      <c r="B20" s="6" t="inlineStr"/>
-      <c r="C20" s="6" t="inlineStr"/>
-      <c r="D20" s="6" t="inlineStr"/>
+      <c r="A20" s="5" t="inlineStr"/>
+      <c r="B20" s="5" t="inlineStr"/>
+      <c r="C20" s="5" t="inlineStr"/>
+      <c r="D20" s="5" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr"/>
-      <c r="B21" s="6" t="inlineStr"/>
-      <c r="C21" s="6" t="inlineStr"/>
-      <c r="D21" s="6" t="inlineStr"/>
+      <c r="A21" s="5" t="inlineStr"/>
+      <c r="B21" s="5" t="inlineStr"/>
+      <c r="C21" s="5" t="inlineStr"/>
+      <c r="D21" s="5" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="inlineStr"/>
-      <c r="B22" s="6" t="inlineStr"/>
-      <c r="C22" s="6" t="inlineStr"/>
-      <c r="D22" s="6" t="inlineStr"/>
+      <c r="A22" s="5" t="inlineStr"/>
+      <c r="B22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="inlineStr"/>
+      <c r="D22" s="5" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="inlineStr"/>
-      <c r="B23" s="6" t="inlineStr"/>
-      <c r="C23" s="6" t="inlineStr"/>
-      <c r="D23" s="6" t="inlineStr"/>
+      <c r="A23" s="5" t="inlineStr"/>
+      <c r="B23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="inlineStr"/>
+      <c r="D23" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3202,7 +3356,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3223,7 +3377,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>PLAIN / DIAMOND (Same rates)</t>
         </is>
@@ -3245,46 +3399,46 @@
       <c r="A5" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B5" s="6" t="inlineStr"/>
+      <c r="B5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B6" s="6" t="inlineStr"/>
+      <c r="B6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B7" s="6" t="inlineStr"/>
+      <c r="B7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B8" s="6" t="inlineStr"/>
+      <c r="B8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B9" s="6" t="inlineStr"/>
+      <c r="B9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="B10" s="6" t="inlineStr"/>
+      <c r="B10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="B11" s="6" t="inlineStr"/>
+      <c r="B11" s="5" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>CERAMIC</t>
         </is>
@@ -3306,19 +3460,19 @@
       <c r="A16" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="6" t="inlineStr"/>
+      <c r="B16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B17" s="6" t="inlineStr"/>
+      <c r="B17" s="5" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="B18" s="6" t="inlineStr"/>
+      <c r="B18" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/backend/static/pulley_pricing_template.xlsx
+++ b/backend/static/pulley_pricing_template.xlsx
@@ -9,11 +9,10 @@
   <sheets>
     <sheet name="1. Pipe Pricing" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="2. Shaft Pricing" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="3. Shaft Dia @ Bearing" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="4. End Plate" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="5. Hub Pricing" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="6. KLA (LATER)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="7. Rubber Lagging" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="3. End Plate" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="4. Hub Pricing" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="5. KLA (LATER)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="6. Rubber Lagging" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -46,10 +45,6 @@
     </font>
     <font>
       <color rgb="00996600"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FF0000"/>
     </font>
   </fonts>
   <fills count="5">
@@ -96,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,7 +110,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1562,7 +1556,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SHAFT PRICING - RATE PER KG (₹/kg) - Shaft Dia × Material</t>
+          <t>SHAFT PRICING - RATE PER KG (₹/kg)</t>
         </is>
       </c>
     </row>
@@ -2055,21 +2049,21 @@
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>Total: 51 shaft diameters × 4 materials = 204 combinations</t>
+          <t>Total: 51 shaft diameters × 4 materials</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>Yellow cells = Enter rate (₹/kg) for each combination</t>
+          <t>Yellow cells = Enter rate (₹/kg)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Shaft Length: Manual entry by user (not in this table)</t>
+          <t>Note: Shaft Dia @ Bearing is for selection only, not for pricing</t>
         </is>
       </c>
     </row>
@@ -2087,476 +2081,243 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B61"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SHAFT DIA @ BEARING (for reference)</t>
+          <t>END PLATE PRICING</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
-        <is>
-          <t>NOTE: Bearing Dia must always be LESS than Centre Dia</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Material: MS</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Diameter: Same as Pipe Dia</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>MS Rate (₹/kg):</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>THICKNESSES (mm):</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Sr.</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Shaft Dia @ Bearing (mm)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>40</v>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Thickness (mm)</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B10" s="4" t="n">
-        <v>45</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B11" s="4" t="n">
-        <v>50</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B12" s="4" t="n">
-        <v>55</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B13" s="4" t="n">
-        <v>60</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B14" s="4" t="n">
-        <v>65</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B15" s="4" t="n">
-        <v>70</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B16" s="4" t="n">
-        <v>75</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B17" s="4" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B18" s="4" t="n">
-        <v>85</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B19" s="4" t="n">
-        <v>90</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B20" s="4" t="n">
-        <v>95</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B21" s="4" t="n">
-        <v>100</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B22" s="4" t="n">
-        <v>105</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B23" s="4" t="n">
-        <v>110</v>
+        <v>32</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B24" s="4" t="n">
-        <v>115</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B25" s="4" t="n">
-        <v>120</v>
+        <v>36</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B26" s="4" t="n">
-        <v>125</v>
+        <v>38</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B27" s="4" t="n">
-        <v>130</v>
+        <v>40</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B28" s="4" t="n">
-        <v>135</v>
+        <v>42</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B29" s="4" t="n">
-        <v>140</v>
+        <v>44</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B30" s="4" t="n">
-        <v>145</v>
+        <v>46</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B31" s="4" t="n">
-        <v>150</v>
+        <v>48</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B32" s="4" t="n">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="B33" s="4" t="n">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="B34" s="4" t="n">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="B35" s="4" t="n">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="n">
-        <v>31</v>
-      </c>
-      <c r="B36" s="4" t="n">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="B37" s="4" t="n">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="n">
-        <v>33</v>
-      </c>
-      <c r="B38" s="4" t="n">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="B39" s="4" t="n">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="B40" s="4" t="n">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="n">
-        <v>36</v>
-      </c>
-      <c r="B41" s="4" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="n">
-        <v>37</v>
-      </c>
-      <c r="B42" s="4" t="n">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="n">
-        <v>38</v>
-      </c>
-      <c r="B43" s="4" t="n">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="3" t="n">
-        <v>39</v>
-      </c>
-      <c r="B44" s="4" t="n">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="B45" s="4" t="n">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="n">
-        <v>41</v>
-      </c>
-      <c r="B46" s="4" t="n">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="B47" s="4" t="n">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="3" t="n">
-        <v>43</v>
-      </c>
-      <c r="B48" s="4" t="n">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="3" t="n">
-        <v>44</v>
-      </c>
-      <c r="B49" s="4" t="n">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="3" t="n">
-        <v>45</v>
-      </c>
-      <c r="B50" s="4" t="n">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="3" t="n">
-        <v>46</v>
-      </c>
-      <c r="B51" s="4" t="n">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="3" t="n">
-        <v>47</v>
-      </c>
-      <c r="B52" s="4" t="n">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="n">
-        <v>48</v>
-      </c>
-      <c r="B53" s="4" t="n">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="n">
-        <v>49</v>
-      </c>
-      <c r="B54" s="4" t="n">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="3" t="n">
         <v>50</v>
-      </c>
-      <c r="B55" s="4" t="n">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="3" t="n">
-        <v>51</v>
-      </c>
-      <c r="B56" s="4" t="n">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="3" t="n">
-        <v>52</v>
-      </c>
-      <c r="B57" s="4" t="n">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="3" t="n">
-        <v>53</v>
-      </c>
-      <c r="B58" s="4" t="n">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="3" t="n">
-        <v>54</v>
-      </c>
-      <c r="B59" s="4" t="n">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Total: 54 sizes</t>
-        </is>
       </c>
     </row>
   </sheetData>
@@ -2573,17 +2334,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:B47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>END PLATE PRICING</t>
+          <t>HUB PRICING</t>
         </is>
       </c>
     </row>
@@ -2597,7 +2358,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Diameter: Same as Pipe Dia</t>
+          <t>Options: No Hub / With Hub</t>
         </is>
       </c>
     </row>
@@ -2612,7 +2373,7 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>THICKNESSES (mm):</t>
+          <t>HUB DIAMETERS (mm):</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2385,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Thickness (mm)</t>
+          <t>Hub Dia (mm)</t>
         </is>
       </c>
     </row>
@@ -2633,7 +2394,7 @@
         <v>1</v>
       </c>
       <c r="B10" s="4" t="n">
-        <v>6</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11">
@@ -2641,7 +2402,7 @@
         <v>2</v>
       </c>
       <c r="B11" s="4" t="n">
-        <v>8</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12">
@@ -2649,7 +2410,7 @@
         <v>3</v>
       </c>
       <c r="B12" s="4" t="n">
-        <v>10</v>
+        <v>120</v>
       </c>
     </row>
     <row r="13">
@@ -2657,7 +2418,7 @@
         <v>4</v>
       </c>
       <c r="B13" s="4" t="n">
-        <v>12</v>
+        <v>130</v>
       </c>
     </row>
     <row r="14">
@@ -2665,7 +2426,7 @@
         <v>5</v>
       </c>
       <c r="B14" s="4" t="n">
-        <v>14</v>
+        <v>140</v>
       </c>
     </row>
     <row r="15">
@@ -2673,7 +2434,7 @@
         <v>6</v>
       </c>
       <c r="B15" s="4" t="n">
-        <v>16</v>
+        <v>150</v>
       </c>
     </row>
     <row r="16">
@@ -2681,7 +2442,7 @@
         <v>7</v>
       </c>
       <c r="B16" s="4" t="n">
-        <v>18</v>
+        <v>160</v>
       </c>
     </row>
     <row r="17">
@@ -2689,7 +2450,7 @@
         <v>8</v>
       </c>
       <c r="B17" s="4" t="n">
-        <v>20</v>
+        <v>170</v>
       </c>
     </row>
     <row r="18">
@@ -2697,7 +2458,7 @@
         <v>9</v>
       </c>
       <c r="B18" s="4" t="n">
-        <v>22</v>
+        <v>180</v>
       </c>
     </row>
     <row r="19">
@@ -2705,7 +2466,7 @@
         <v>10</v>
       </c>
       <c r="B19" s="4" t="n">
-        <v>24</v>
+        <v>190</v>
       </c>
     </row>
     <row r="20">
@@ -2713,7 +2474,7 @@
         <v>11</v>
       </c>
       <c r="B20" s="4" t="n">
-        <v>26</v>
+        <v>200</v>
       </c>
     </row>
     <row r="21">
@@ -2721,7 +2482,7 @@
         <v>12</v>
       </c>
       <c r="B21" s="4" t="n">
-        <v>28</v>
+        <v>210</v>
       </c>
     </row>
     <row r="22">
@@ -2729,7 +2490,7 @@
         <v>13</v>
       </c>
       <c r="B22" s="4" t="n">
-        <v>30</v>
+        <v>220</v>
       </c>
     </row>
     <row r="23">
@@ -2737,7 +2498,7 @@
         <v>14</v>
       </c>
       <c r="B23" s="4" t="n">
-        <v>32</v>
+        <v>230</v>
       </c>
     </row>
     <row r="24">
@@ -2745,7 +2506,7 @@
         <v>15</v>
       </c>
       <c r="B24" s="4" t="n">
-        <v>34</v>
+        <v>240</v>
       </c>
     </row>
     <row r="25">
@@ -2753,7 +2514,7 @@
         <v>16</v>
       </c>
       <c r="B25" s="4" t="n">
-        <v>36</v>
+        <v>250</v>
       </c>
     </row>
     <row r="26">
@@ -2761,7 +2522,7 @@
         <v>17</v>
       </c>
       <c r="B26" s="4" t="n">
-        <v>38</v>
+        <v>260</v>
       </c>
     </row>
     <row r="27">
@@ -2769,7 +2530,7 @@
         <v>18</v>
       </c>
       <c r="B27" s="4" t="n">
-        <v>40</v>
+        <v>270</v>
       </c>
     </row>
     <row r="28">
@@ -2777,7 +2538,7 @@
         <v>19</v>
       </c>
       <c r="B28" s="4" t="n">
-        <v>42</v>
+        <v>280</v>
       </c>
     </row>
     <row r="29">
@@ -2785,7 +2546,7 @@
         <v>20</v>
       </c>
       <c r="B29" s="4" t="n">
-        <v>44</v>
+        <v>290</v>
       </c>
     </row>
     <row r="30">
@@ -2793,7 +2554,7 @@
         <v>21</v>
       </c>
       <c r="B30" s="4" t="n">
-        <v>46</v>
+        <v>300</v>
       </c>
     </row>
     <row r="31">
@@ -2801,7 +2562,7 @@
         <v>22</v>
       </c>
       <c r="B31" s="4" t="n">
-        <v>48</v>
+        <v>310</v>
       </c>
     </row>
     <row r="32">
@@ -2809,7 +2570,118 @@
         <v>23</v>
       </c>
       <c r="B32" s="4" t="n">
-        <v>50</v>
+        <v>320</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="B33" s="4" t="n">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="B34" s="4" t="n">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="B35" s="4" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="B36" s="4" t="n">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="B37" s="4" t="n">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="B38" s="4" t="n">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="B39" s="4" t="n">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="B40" s="4" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="B41" s="4" t="n">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="B42" s="4" t="n">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="B43" s="4" t="n">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="B44" s="4" t="n">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="B45" s="4" t="n">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Hub Length: Manual entry</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -2821,370 +2693,6 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B47"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>HUB PRICING</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Material: MS</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Options: No Hub / With Hub</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>MS Rate (₹/kg):</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>HUB DIAMETERS (mm):</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Sr.</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Hub Dia (mm)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B10" s="4" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B11" s="4" t="n">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B12" s="4" t="n">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="B13" s="4" t="n">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="B14" s="4" t="n">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="B15" s="4" t="n">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="B16" s="4" t="n">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="B17" s="4" t="n">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="B18" s="4" t="n">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="B19" s="4" t="n">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="B20" s="4" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="B21" s="4" t="n">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="B22" s="4" t="n">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="B23" s="4" t="n">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="B24" s="4" t="n">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="B25" s="4" t="n">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="B26" s="4" t="n">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="B27" s="4" t="n">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="B28" s="4" t="n">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="B29" s="4" t="n">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="B30" s="4" t="n">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="B31" s="4" t="n">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="B32" s="4" t="n">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="B33" s="4" t="n">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="B34" s="4" t="n">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="B35" s="4" t="n">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="n">
-        <v>27</v>
-      </c>
-      <c r="B36" s="4" t="n">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="B37" s="4" t="n">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="B38" s="4" t="n">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="B39" s="4" t="n">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="n">
-        <v>31</v>
-      </c>
-      <c r="B40" s="4" t="n">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="B41" s="4" t="n">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="n">
-        <v>33</v>
-      </c>
-      <c r="B42" s="4" t="n">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="B43" s="4" t="n">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="B44" s="4" t="n">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="n">
-        <v>36</v>
-      </c>
-      <c r="B45" s="4" t="n">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Hub Length: Manual entry</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3356,7 +2864,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/backend/static/pulley_pricing_template.xlsx
+++ b/backend/static/pulley_pricing_template.xlsx
@@ -11,8 +11,9 @@
     <sheet name="2. Shaft Pricing" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="3. End Plate" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="4. Hub Pricing" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="5. KLA (LATER)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="5. KLA Pricing" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="6. Rubber Lagging" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="7. Summary" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -45,6 +46,10 @@
     </font>
     <font>
       <color rgb="00996600"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="5">
@@ -91,7 +96,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -110,6 +115,7 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1543,7 +1549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E60"/>
+  <dimension ref="A1:E58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2057,13 +2063,6 @@
       <c r="A58" s="7" t="inlineStr">
         <is>
           <t>Yellow cells = Enter rate (₹/kg)</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Note: Shaft Dia @ Bearing is for selection only, not for pricing</t>
         </is>
       </c>
     </row>
@@ -2334,11 +2333,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B47"/>
+  <dimension ref="A1:C50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2349,336 +2349,365 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Material: MS</t>
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>HUB TYPES:</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Options: No Hub / With Hub</t>
+          <t>1. No Hub</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>→ No additional cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2. With Hub</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>→ Hub Dia + Hub Length → Weight × MS Rate</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MS Rate (₹/kg):</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>HUB DIAMETERS (mm):</t>
+          <t>3. KLA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>→ Shaft Dia @ Hub → KLA Model → Fixed Price</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>WITH HUB - MS Rate (₹/kg):</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Hub Diameters (mm):</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Sr.</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Hub Dia (mm)</t>
         </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B10" s="4" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B11" s="4" t="n">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B12" s="4" t="n">
-        <v>120</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B13" s="4" t="n">
-        <v>130</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B14" s="4" t="n">
-        <v>140</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B15" s="4" t="n">
-        <v>150</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B16" s="4" t="n">
-        <v>160</v>
+        <v>130</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B17" s="4" t="n">
-        <v>170</v>
+        <v>140</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B18" s="4" t="n">
-        <v>180</v>
+        <v>150</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B19" s="4" t="n">
-        <v>190</v>
+        <v>160</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B20" s="4" t="n">
-        <v>200</v>
+        <v>170</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B21" s="4" t="n">
-        <v>210</v>
+        <v>180</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B22" s="4" t="n">
-        <v>220</v>
+        <v>190</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B23" s="4" t="n">
-        <v>230</v>
+        <v>200</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B24" s="4" t="n">
-        <v>240</v>
+        <v>210</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B25" s="4" t="n">
-        <v>250</v>
+        <v>220</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B26" s="4" t="n">
-        <v>260</v>
+        <v>230</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B27" s="4" t="n">
-        <v>270</v>
+        <v>240</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B28" s="4" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B29" s="4" t="n">
-        <v>290</v>
+        <v>260</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B30" s="4" t="n">
-        <v>300</v>
+        <v>270</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B31" s="4" t="n">
-        <v>310</v>
+        <v>280</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B32" s="4" t="n">
-        <v>320</v>
+        <v>290</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B33" s="4" t="n">
-        <v>330</v>
+        <v>300</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B34" s="4" t="n">
-        <v>340</v>
+        <v>310</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B35" s="4" t="n">
-        <v>350</v>
+        <v>320</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B36" s="4" t="n">
-        <v>360</v>
+        <v>330</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B37" s="4" t="n">
-        <v>370</v>
+        <v>340</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B38" s="4" t="n">
-        <v>380</v>
+        <v>350</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B39" s="4" t="n">
-        <v>390</v>
+        <v>360</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B40" s="4" t="n">
-        <v>400</v>
+        <v>370</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B41" s="4" t="n">
-        <v>410</v>
+        <v>380</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B42" s="4" t="n">
-        <v>420</v>
+        <v>390</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B43" s="4" t="n">
-        <v>430</v>
+        <v>400</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B44" s="4" t="n">
-        <v>440</v>
+        <v>410</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="B45" s="4" t="n">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="B46" s="4" t="n">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="B47" s="4" t="n">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="n">
         <v>36</v>
       </c>
-      <c r="B45" s="4" t="n">
+      <c r="B48" s="4" t="n">
         <v>450</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
+    <row r="50">
+      <c r="A50" t="inlineStr">
         <is>
           <t>Hub Length: Manual entry</t>
         </is>
@@ -2686,7 +2715,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A1:C1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2698,163 +2727,633 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:G63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="5" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>KLA PRICING - TO FILL LATER</t>
+          <t>KLA (KEYLESS LOCKING ASSEMBLY) PRICING</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>When Hub Type = KLA:</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1. User selects Shaft Dia @ Hub (25-290mm, must be &lt; Shaft Dia)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2. KLA Model is determined based on Shaft Dia @ Hub</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>3. Price = Fixed price per KLA Model</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>SHAFT DIA @ HUB OPTIONS:</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>KLA MODELS &amp; PRICING:</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Sr.</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Shaft Dia @ Hub (mm)</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>KLA Model</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Min Shaft @ Brg</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Max Shaft @ Brg</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Min Shaft @ Hub</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Max Shaft @ Hub</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>Price (₹)</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr"/>
-      <c r="B4" s="5" t="inlineStr"/>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr"/>
-      <c r="B5" s="5" t="inlineStr"/>
-      <c r="C5" s="5" t="inlineStr"/>
-      <c r="D5" s="5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr"/>
-      <c r="B6" s="5" t="inlineStr"/>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr"/>
-      <c r="B7" s="5" t="inlineStr"/>
-      <c r="C7" s="5" t="inlineStr"/>
-      <c r="D7" s="5" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr"/>
-      <c r="B8" s="5" t="inlineStr"/>
-      <c r="C8" s="5" t="inlineStr"/>
-      <c r="D8" s="5" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr"/>
-      <c r="B9" s="5" t="inlineStr"/>
-      <c r="C9" s="5" t="inlineStr"/>
-      <c r="D9" s="5" t="inlineStr"/>
-    </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr"/>
-      <c r="B10" s="5" t="inlineStr"/>
-      <c r="C10" s="5" t="inlineStr"/>
+      <c r="A10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>25</v>
+      </c>
       <c r="D10" s="5" t="inlineStr"/>
+      <c r="E10" s="5" t="inlineStr"/>
+      <c r="F10" s="5" t="inlineStr"/>
+      <c r="G10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr"/>
-      <c r="B11" s="5" t="inlineStr"/>
-      <c r="C11" s="5" t="inlineStr"/>
+      <c r="A11" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>30</v>
+      </c>
       <c r="D11" s="5" t="inlineStr"/>
+      <c r="E11" s="5" t="inlineStr"/>
+      <c r="F11" s="5" t="inlineStr"/>
+      <c r="G11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr"/>
-      <c r="B12" s="5" t="inlineStr"/>
-      <c r="C12" s="5" t="inlineStr"/>
+      <c r="A12" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>35</v>
+      </c>
       <c r="D12" s="5" t="inlineStr"/>
+      <c r="E12" s="5" t="inlineStr"/>
+      <c r="F12" s="5" t="inlineStr"/>
+      <c r="G12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr"/>
-      <c r="B13" s="5" t="inlineStr"/>
-      <c r="C13" s="5" t="inlineStr"/>
+      <c r="A13" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>40</v>
+      </c>
       <c r="D13" s="5" t="inlineStr"/>
+      <c r="E13" s="5" t="inlineStr"/>
+      <c r="F13" s="5" t="inlineStr"/>
+      <c r="G13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr"/>
-      <c r="B14" s="5" t="inlineStr"/>
-      <c r="C14" s="5" t="inlineStr"/>
+      <c r="A14" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>45</v>
+      </c>
       <c r="D14" s="5" t="inlineStr"/>
+      <c r="E14" s="5" t="inlineStr"/>
+      <c r="F14" s="5" t="inlineStr"/>
+      <c r="G14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr"/>
-      <c r="B15" s="5" t="inlineStr"/>
-      <c r="C15" s="5" t="inlineStr"/>
+      <c r="A15" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>50</v>
+      </c>
       <c r="D15" s="5" t="inlineStr"/>
+      <c r="E15" s="5" t="inlineStr"/>
+      <c r="F15" s="5" t="inlineStr"/>
+      <c r="G15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr"/>
-      <c r="B16" s="5" t="inlineStr"/>
-      <c r="C16" s="5" t="inlineStr"/>
+      <c r="A16" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>55</v>
+      </c>
       <c r="D16" s="5" t="inlineStr"/>
+      <c r="E16" s="5" t="inlineStr"/>
+      <c r="F16" s="5" t="inlineStr"/>
+      <c r="G16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr"/>
-      <c r="B17" s="5" t="inlineStr"/>
-      <c r="C17" s="5" t="inlineStr"/>
+      <c r="A17" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>60</v>
+      </c>
       <c r="D17" s="5" t="inlineStr"/>
+      <c r="E17" s="5" t="inlineStr"/>
+      <c r="F17" s="5" t="inlineStr"/>
+      <c r="G17" s="5" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr"/>
-      <c r="B18" s="5" t="inlineStr"/>
-      <c r="C18" s="5" t="inlineStr"/>
+      <c r="A18" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>65</v>
+      </c>
       <c r="D18" s="5" t="inlineStr"/>
+      <c r="E18" s="5" t="inlineStr"/>
+      <c r="F18" s="5" t="inlineStr"/>
+      <c r="G18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr"/>
-      <c r="B19" s="5" t="inlineStr"/>
-      <c r="C19" s="5" t="inlineStr"/>
+      <c r="A19" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>70</v>
+      </c>
       <c r="D19" s="5" t="inlineStr"/>
+      <c r="E19" s="5" t="inlineStr"/>
+      <c r="F19" s="5" t="inlineStr"/>
+      <c r="G19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr"/>
-      <c r="B20" s="5" t="inlineStr"/>
-      <c r="C20" s="5" t="inlineStr"/>
+      <c r="A20" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>75</v>
+      </c>
       <c r="D20" s="5" t="inlineStr"/>
+      <c r="E20" s="5" t="inlineStr"/>
+      <c r="F20" s="5" t="inlineStr"/>
+      <c r="G20" s="5" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr"/>
-      <c r="B21" s="5" t="inlineStr"/>
-      <c r="C21" s="5" t="inlineStr"/>
+      <c r="A21" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>80</v>
+      </c>
       <c r="D21" s="5" t="inlineStr"/>
+      <c r="E21" s="5" t="inlineStr"/>
+      <c r="F21" s="5" t="inlineStr"/>
+      <c r="G21" s="5" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr"/>
-      <c r="B22" s="5" t="inlineStr"/>
-      <c r="C22" s="5" t="inlineStr"/>
+      <c r="A22" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>85</v>
+      </c>
       <c r="D22" s="5" t="inlineStr"/>
+      <c r="E22" s="5" t="inlineStr"/>
+      <c r="F22" s="5" t="inlineStr"/>
+      <c r="G22" s="5" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr"/>
-      <c r="B23" s="5" t="inlineStr"/>
-      <c r="C23" s="5" t="inlineStr"/>
+      <c r="A23" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B23" s="4" t="n">
+        <v>90</v>
+      </c>
       <c r="D23" s="5" t="inlineStr"/>
+      <c r="E23" s="5" t="inlineStr"/>
+      <c r="F23" s="5" t="inlineStr"/>
+      <c r="G23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="B24" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="D24" s="5" t="inlineStr"/>
+      <c r="E24" s="5" t="inlineStr"/>
+      <c r="F24" s="5" t="inlineStr"/>
+      <c r="G24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="B25" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="D25" s="5" t="inlineStr"/>
+      <c r="E25" s="5" t="inlineStr"/>
+      <c r="F25" s="5" t="inlineStr"/>
+      <c r="G25" s="5" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="B26" s="4" t="n">
+        <v>105</v>
+      </c>
+      <c r="D26" s="5" t="inlineStr"/>
+      <c r="E26" s="5" t="inlineStr"/>
+      <c r="F26" s="5" t="inlineStr"/>
+      <c r="G26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B27" s="4" t="n">
+        <v>110</v>
+      </c>
+      <c r="D27" s="5" t="inlineStr"/>
+      <c r="E27" s="5" t="inlineStr"/>
+      <c r="F27" s="5" t="inlineStr"/>
+      <c r="G27" s="5" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="B28" s="4" t="n">
+        <v>115</v>
+      </c>
+      <c r="D28" s="5" t="inlineStr"/>
+      <c r="E28" s="5" t="inlineStr"/>
+      <c r="F28" s="5" t="inlineStr"/>
+      <c r="G28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B29" s="4" t="n">
+        <v>120</v>
+      </c>
+      <c r="D29" s="5" t="inlineStr"/>
+      <c r="E29" s="5" t="inlineStr"/>
+      <c r="F29" s="5" t="inlineStr"/>
+      <c r="G29" s="5" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B30" s="4" t="n">
+        <v>125</v>
+      </c>
+      <c r="D30" s="5" t="inlineStr"/>
+      <c r="E30" s="5" t="inlineStr"/>
+      <c r="F30" s="5" t="inlineStr"/>
+      <c r="G30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B31" s="4" t="n">
+        <v>130</v>
+      </c>
+      <c r="D31" s="5" t="inlineStr"/>
+      <c r="E31" s="5" t="inlineStr"/>
+      <c r="F31" s="5" t="inlineStr"/>
+      <c r="G31" s="5" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="B32" s="4" t="n">
+        <v>135</v>
+      </c>
+      <c r="D32" s="5" t="inlineStr"/>
+      <c r="E32" s="5" t="inlineStr"/>
+      <c r="F32" s="5" t="inlineStr"/>
+      <c r="G32" s="5" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="B33" s="4" t="n">
+        <v>140</v>
+      </c>
+      <c r="D33" s="5" t="inlineStr"/>
+      <c r="E33" s="5" t="inlineStr"/>
+      <c r="F33" s="5" t="inlineStr"/>
+      <c r="G33" s="5" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="B34" s="4" t="n">
+        <v>145</v>
+      </c>
+      <c r="D34" s="5" t="inlineStr"/>
+      <c r="E34" s="5" t="inlineStr"/>
+      <c r="F34" s="5" t="inlineStr"/>
+      <c r="G34" s="5" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="B35" s="4" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="B36" s="4" t="n">
+        <v>155</v>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>Yellow cells = Enter KLA models and prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="B37" s="4" t="n">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="B38" s="4" t="n">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="B39" s="4" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="B40" s="4" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="B41" s="4" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="B42" s="4" t="n">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="B43" s="4" t="n">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="B44" s="4" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="B45" s="4" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="B46" s="4" t="n">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="B47" s="4" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="B48" s="4" t="n">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="B49" s="4" t="n">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="B50" s="4" t="n">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="B51" s="4" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="B52" s="4" t="n">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="B53" s="4" t="n">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="B54" s="4" t="n">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="B55" s="4" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="B56" s="4" t="n">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="B57" s="4" t="n">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="B58" s="4" t="n">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="B59" s="4" t="n">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="B60" s="4" t="n">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="B61" s="4" t="n">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="n">
+        <v>53</v>
+      </c>
+      <c r="B62" s="4" t="n">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="n">
+        <v>54</v>
+      </c>
+      <c r="B63" s="4" t="n">
+        <v>290</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2988,4 +3487,332 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>PULLEY CONFIGURATION SUMMARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>PULLEY TYPES</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Drive, Tail, Bend, Snub, Take-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>PIPE</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Diameters</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>139, 152, 168, 193, 219, 245, 273, 323, 355, 406, 455, 508, 609, 630, 800, 1000 mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Thickness</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>4.8 to 26mm (varies by diameter)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Length</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Manual entry</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Pricing</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Fixed rate per Dia+Thk combination (₹/kg)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>SHAFT</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Diameter</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>50, 55, 60... 300mm (5mm gaps)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Materials</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>MS, EN-8, EN-9, EN-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Length</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Manual entry</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Pricing</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Fixed rate per Dia+Material combination (₹/kg)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>END PLATE</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Material</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Diameter</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Same as Pipe Diameter</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Thickness</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>6, 8, 10... 50mm (2mm gaps)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Pricing</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Weight × MS Rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>HUB OPTIONS</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  1. No Hub</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>No additional cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  2. With Hub</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Hub Dia (100-450mm) + Hub Length → Weight × MS Rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  3. KLA</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Shaft Dia @ Hub (25-290mm) → KLA Model → Fixed Price</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>RUBBER LAGGING</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Types</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>None / Plain / Diamond / Ceramic</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Plain/Diamond</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>8, 10, 12, 14, 16, 18, 20mm (same rates)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Ceramic</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>12, 15, 22mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Pricing</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Area (π × Dia × Length) × Rate per sqm</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>